--- a/reports/pdf_rolling5_20261026.xlsx
+++ b/reports/pdf_rolling5_20261026.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K131"/>
+  <dimension ref="A1:K167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -562,14 +562,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-10-19 ~ 2026-10-26  (최근 5거래일)  ·  캡처 6/10  ·  대기: RISE, TIGER, TIGER, MIDAS</t>
+          <t>최근 5거래일 변화  ·  2026-10-19 ~ 2026-10-26  (최근 5거래일)  ·  캡처 9/10  ·  대기: RISE</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,380억   ·   현금 16억(0.4%)      오늘 2026-10-26  vs  5일전 2026-10-19      매수 17종목  /  매도 13종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,331억      오늘 2026-10-26  vs  5일전 2026-10-19      매수 17종목  /  매도 13종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,7 +665,7 @@
         <v>513</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>4956195899</v>
+        <v>4946244793</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         <v>-176</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1647782499</v>
+        <v>-1644474063</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>142</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>3295365799</v>
+        <v>3288749326</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>-156</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1981044119</v>
+        <v>-1977066557</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>113</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>7315620441</v>
+        <v>7300932057</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>-83</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-2178301931</v>
+        <v>-2173928312</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>104</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>4500725071</v>
+        <v>4491688465</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>-68</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-4172045051</v>
+        <v>-4163668373</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>79</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>1597285296</v>
+        <v>1594078249</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>-46</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-2254147336</v>
+        <v>-2249621434</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>76</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>2259525736</v>
+        <v>2254989035</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>-26</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-408379945</v>
+        <v>-407559995</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>63</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>811959169</v>
+        <v>810328908</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>-25</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1114275067</v>
+        <v>-1112037813</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>60</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>2644380159</v>
+        <v>2639070743</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>-19</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-2806429369</v>
+        <v>-2800794589</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>32</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1298784078</v>
+        <v>1296176365</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>-11</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-2815692170</v>
+        <v>-2810038792</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>31</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>2559620554</v>
+        <v>2554481320</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>-7</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-768314446</v>
+        <v>-766771816</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>29</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>419973385</v>
+        <v>419130158</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>-6</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-118802887</v>
+        <v>-118564353</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>25</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1302270078</v>
+        <v>1299655366</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>-5</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-1048290063</v>
+        <v>-1046185295</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1186,23 +1186,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>2844576171</v>
+        <v>403166514</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>1.45%→2.03%</t>
+          <t>1.43%→1.44%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>25→37</t>
+          <t>173→185</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1214,7 +1214,7 @@
         <v>-4</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-690427242</v>
+        <v>-689040994</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>12</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>561146434</v>
+        <v>560019758</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1258,23 +1258,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>403977624</v>
+        <v>2838864800</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>1.43%→1.44%</t>
+          <t>1.45%→2.03%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>173→185</t>
+          <t>25→37</t>
         </is>
       </c>
       <c r="G20" s="17" t="n"/>
@@ -1293,7 +1293,7 @@
         <v>9</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>2012418121</v>
+        <v>2008377566</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>8</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>823094450</v>
+        <v>821441831</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,140억   ·   현금 61억(2.0%)      오늘 2026-10-26  vs  5일전 2026-10-19      매수 8종목  /  매도 16종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,109억      오늘 2026-10-26  vs  5일전 2026-10-19      매수 8종목  /  매도 16종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1438,7 +1438,7 @@
         <v>141</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>3763134620</v>
+        <v>3763135040</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>-118</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-1489100889</v>
+        <v>-1489101055</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>104</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>4730325248</v>
+        <v>4730325776</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>-113</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-2472750566</v>
+        <v>-2472750842</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>65</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1544546135</v>
+        <v>1544546308</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>-58</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-1252069107</v>
+        <v>-1252069247</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>39</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>1610516580</v>
+        <v>1610516760</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>-43</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-5183929114</v>
+        <v>-5183929693</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>13</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>922888131</v>
+        <v>922888234</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>-38</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-2107939643</v>
+        <v>-2107939879</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>12</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>9446903296</v>
+        <v>9446904352</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>-33</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-1208572110</v>
+        <v>-1208572245</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>9</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>939535130</v>
+        <v>939535235</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>-32</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-3094838169</v>
+        <v>-3094838515</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>6</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>151595089</v>
+        <v>151595106</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>-26</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-178015487</v>
+        <v>-178015507</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>-25</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-289308728</v>
+        <v>-289308761</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>-24</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-480077964</v>
+        <v>-480078018</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>-22</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-1062078521</v>
+        <v>-1062078640</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>-22</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-2829452789</v>
+        <v>-2829453105</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>-18</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-153882709</v>
+        <v>-153882726</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>-7</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-1358878399</v>
+        <v>-1358878551</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>-6</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-27934738</v>
+        <v>-27934741</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>-4</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-58425596</v>
+        <v>-58425602</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
     <row r="44" ht="19" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,218억   ·   현금 45억(2.1%)      오늘 2026-10-26  vs  5일전 2026-10-19      매수 20종목  /  매도 31종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,181억      오늘 2026-10-26  vs  5일전 2026-10-19      매수 20종목  /  매도 31종목</t>
         </is>
       </c>
       <c r="B44" s="4" t="n"/>
@@ -2103,7 +2103,7 @@
         <v>1000</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>7358995986</v>
+        <v>7359004014</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>-248</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-7807531741</v>
+        <v>-7807540259</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>500</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>7820995734</v>
+        <v>7821004266</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>-202</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-1207878541</v>
+        <v>-1207879859</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>280</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>12917512954</v>
+        <v>12917527046</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>-129</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-4776351395</v>
+        <v>-4776356605</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>250</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>6583496409</v>
+        <v>6583503591</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>-121</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-1099671600</v>
+        <v>-1099672800</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>250</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>6690746350</v>
+        <v>6690753650</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>-118</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-1030351838</v>
+        <v>-1030352962</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>199</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>12372221252</v>
+        <v>12372234748</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>-112</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-1122104988</v>
+        <v>-1122106212</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>151</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>1383280045</v>
+        <v>1383281555</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>-110</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-2112658848</v>
+        <v>-2112661152</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>150</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>3460048113</v>
+        <v>3460051887</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>-108</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-2555386606</v>
+        <v>-2555389394</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>135</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>1995838911</v>
+        <v>1995841089</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
@@ -2469,23 +2469,23 @@
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
         <v>-105</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-7636855834</v>
+        <v>-5391542941</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>4.63%→0.85%</t>
+          <t>4.01%→1.80%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>130→25</t>
+          <t>180→75</t>
         </is>
       </c>
     </row>
@@ -2499,7 +2499,7 @@
         <v>120</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>5520236989</v>
+        <v>5520243011</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
@@ -2513,23 +2513,23 @@
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-105</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-5391537059</v>
+        <v>-7636864166</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>4.01%→1.80%</t>
+          <t>4.63%→0.85%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>180→75</t>
+          <t>130→25</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
         <v>100</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>1709399068</v>
+        <v>1709400932</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>-100</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-1798499019</v>
+        <v>-1798500981</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>99</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>2247694774</v>
+        <v>2247697226</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>-97</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-1856578987</v>
+        <v>-1856581013</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>80</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>6309596558</v>
+        <v>6309603442</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>-66</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-1785959026</v>
+        <v>-1785960974</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>41</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>3071308325</v>
+        <v>3071311675</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
@@ -2689,23 +2689,23 @@
       </c>
       <c r="G60" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>비츠로셀  (편출)</t>
         </is>
       </c>
       <c r="H60" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-5936696762</v>
+        <v>-795300434</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>6.50%→3.34%</t>
+          <t>0.34%→0.00%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
         <is>
-          <t>110→60</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
         <v>35</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>696464620</v>
+        <v>696465380</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
@@ -2733,23 +2733,23 @@
       </c>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>비츠로셀  (편출)</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H61" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-795299566</v>
+        <v>-5936703238</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>0.34%→0.00%</t>
+          <t>6.50%→3.34%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>110→60</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
         <v>28</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>677291631</v>
+        <v>677292369</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
@@ -2777,23 +2777,23 @@
       </c>
       <c r="G62" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="H62" s="15" t="n">
         <v>-49</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-3279274211</v>
+        <v>-2121505157</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>2.86%→1.25%</t>
+          <t>1.91%→1.01%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
         <is>
-          <t>89→40</t>
+          <t>99→50</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
         <v>16</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>2370718707</v>
+        <v>2370721293</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
@@ -2821,46 +2821,46 @@
       </c>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H63" s="15" t="n">
         <v>-49</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-2121502843</v>
+        <v>-3279277789</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>1.91%→1.01%</t>
+          <t>2.86%→1.25%</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
         <is>
-          <t>99→50</t>
+          <t>89→40</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B64" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>1002869453</v>
+        <v>1715670936</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>0.47%→0.91%</t>
+          <t>5.87%→6.43%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>14→29</t>
+          <t>105→120</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
@@ -2872,7 +2872,7 @@
         <v>-44</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-2111206848</v>
+        <v>-2111209152</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
@@ -2888,23 +2888,23 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B65" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>1715669064</v>
+        <v>1002870547</v>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>5.87%→6.43%</t>
+          <t>0.47%→0.91%</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
-          <t>105→120</t>
+          <t>14→29</t>
         </is>
       </c>
       <c r="G65" s="14" t="inlineStr">
@@ -2916,7 +2916,7 @@
         <v>-40</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-2523838623</v>
+        <v>-2523841377</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>6</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>465299746</v>
+        <v>465300254</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>-34</v>
       </c>
       <c r="I66" s="15" t="n">
-        <v>-9065755055</v>
+        <v>-9065764945</v>
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>-27</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>-1915648955</v>
+        <v>-1915651045</v>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
@@ -3009,23 +3009,23 @@
       <c r="E68" s="17" t="n"/>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오  (편출)</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H68" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-715274610</v>
+        <v>-4240502313</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>0.30%→0.00%</t>
+          <t>5.01%→2.78%</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
         <is>
-          <t>25→0</t>
+          <t>60→35</t>
         </is>
       </c>
     </row>
@@ -3037,23 +3037,23 @@
       <c r="E69" s="17" t="n"/>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H69" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-4240497687</v>
+        <v>-1584000864</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>5.01%→2.78%</t>
+          <t>1.45%→0.74%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
         <is>
-          <t>60→35</t>
+          <t>50→25</t>
         </is>
       </c>
     </row>
@@ -3065,23 +3065,23 @@
       <c r="E70" s="17" t="n"/>
       <c r="G70" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>에이비엘바이오  (편출)</t>
         </is>
       </c>
       <c r="H70" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I70" s="15" t="n">
-        <v>-1583999136</v>
+        <v>-715275390</v>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
-          <t>1.45%→0.74%</t>
+          <t>0.30%→0.00%</t>
         </is>
       </c>
       <c r="K70" s="13" t="inlineStr">
         <is>
-          <t>50→25</t>
+          <t>25→0</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
         <v>-24</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>-3563998056</v>
+        <v>-3564001944</v>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>-24</v>
       </c>
       <c r="I72" s="15" t="n">
-        <v>-1080287411</v>
+        <v>-1080288589</v>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>-19</v>
       </c>
       <c r="I73" s="15" t="n">
-        <v>-3266668218</v>
+        <v>-3266671782</v>
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>-15</v>
       </c>
       <c r="I74" s="15" t="n">
-        <v>-1468169199</v>
+        <v>-1468170801</v>
       </c>
       <c r="J74" s="16" t="inlineStr">
         <is>
@@ -3205,23 +3205,23 @@
       <c r="E75" s="17" t="n"/>
       <c r="G75" s="14" t="inlineStr">
         <is>
-          <t>보로노이  (편출)</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H75" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I75" s="15" t="n">
-        <v>-650495645</v>
+        <v>-1861201015</v>
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
-          <t>0.28%→0.00%</t>
+          <t>2.67%→2.07%</t>
         </is>
       </c>
       <c r="K75" s="13" t="inlineStr">
         <is>
-          <t>8→0</t>
+          <t>27→19</t>
         </is>
       </c>
     </row>
@@ -3233,23 +3233,23 @@
       <c r="E76" s="17" t="n"/>
       <c r="G76" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>보로노이  (편출)</t>
         </is>
       </c>
       <c r="H76" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I76" s="15" t="n">
-        <v>-1861198985</v>
+        <v>-650496355</v>
       </c>
       <c r="J76" s="16" t="inlineStr">
         <is>
-          <t>2.67%→2.07%</t>
+          <t>0.28%→0.00%</t>
         </is>
       </c>
       <c r="K76" s="13" t="inlineStr">
         <is>
-          <t>27→19</t>
+          <t>8→0</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
         <v>-7</v>
       </c>
       <c r="I77" s="15" t="n">
-        <v>-1284359299</v>
+        <v>-1284360701</v>
       </c>
       <c r="J77" s="16" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
     <row r="79" ht="19" customHeight="1">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,131억   ·   현금 1억(0.0%)      오늘 2026-10-26  vs  5일전 2026-10-19      매수 5종목  /  매도 3종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,148억      오늘 2026-10-26  vs  5일전 2026-10-19      매수 5종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B79" s="4" t="n"/>
@@ -3380,7 +3380,7 @@
         <v>209</v>
       </c>
       <c r="C82" s="11" t="n">
-        <v>2056016804</v>
+        <v>2056017414</v>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>-389</v>
       </c>
       <c r="I82" s="15" t="n">
-        <v>-3402427737</v>
+        <v>-3402428747</v>
       </c>
       <c r="J82" s="16" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>104</v>
       </c>
       <c r="C83" s="11" t="n">
-        <v>4340253230</v>
+        <v>4340254519</v>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>-303</v>
       </c>
       <c r="I83" s="15" t="n">
-        <v>-4920962887</v>
+        <v>-4920964349</v>
       </c>
       <c r="J83" s="16" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>14</v>
       </c>
       <c r="C84" s="11" t="n">
-        <v>2044644202</v>
+        <v>2044644810</v>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>-62</v>
       </c>
       <c r="I84" s="15" t="n">
-        <v>-1020706101</v>
+        <v>-1020706404</v>
       </c>
       <c r="J84" s="16" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>9</v>
       </c>
       <c r="C85" s="11" t="n">
-        <v>5330376528</v>
+        <v>5330378111</v>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>7</v>
       </c>
       <c r="C86" s="11" t="n">
-        <v>549763254</v>
+        <v>549763418</v>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
     <row r="88" ht="19" customHeight="1">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 248억   ·   현금 2억(0.8%)      오늘 2026-10-26  vs  5일전 2026-10-19      매수 10종목  /  매도 8종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 243억      오늘 2026-10-26  vs  5일전 2026-10-19      매수 10종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B88" s="4" t="n"/>
@@ -3657,11 +3657,11 @@
         <v>345</v>
       </c>
       <c r="C91" s="11" t="n">
-        <v>179951944</v>
+        <v>177743889</v>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>6.52%→7.21%</t>
+          <t>6.56%→7.26%</t>
         </is>
       </c>
       <c r="E91" s="13" t="inlineStr">
@@ -3678,11 +3678,11 @@
         <v>-26</v>
       </c>
       <c r="I91" s="15" t="n">
-        <v>-82284774</v>
+        <v>-76377552</v>
       </c>
       <c r="J91" s="16" t="inlineStr">
         <is>
-          <t>3.34%→2.98%</t>
+          <t>3.16%→2.82%</t>
         </is>
       </c>
       <c r="K91" s="13" t="inlineStr">
@@ -3701,11 +3701,11 @@
         <v>61</v>
       </c>
       <c r="C92" s="11" t="n">
-        <v>93695971</v>
+        <v>97599939</v>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.38%</t>
+          <t>0.00%→0.40%</t>
         </is>
       </c>
       <c r="E92" s="13" t="inlineStr">
@@ -3722,11 +3722,11 @@
         <v>-24</v>
       </c>
       <c r="I92" s="15" t="n">
-        <v>-85862373</v>
+        <v>-86169546</v>
       </c>
       <c r="J92" s="16" t="inlineStr">
         <is>
-          <t>4.67%→4.29%</t>
+          <t>4.77%→4.39%</t>
         </is>
       </c>
       <c r="K92" s="13" t="inlineStr">
@@ -3745,11 +3745,11 @@
         <v>34</v>
       </c>
       <c r="C93" s="11" t="n">
-        <v>30311671</v>
+        <v>28157422</v>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>0.32%→0.45%</t>
+          <t>0.31%→0.42%</t>
         </is>
       </c>
       <c r="E93" s="13" t="inlineStr">
@@ -3766,11 +3766,11 @@
         <v>-22</v>
       </c>
       <c r="I93" s="15" t="n">
-        <v>-42943987</v>
+        <v>-40972774</v>
       </c>
       <c r="J93" s="16" t="inlineStr">
         <is>
-          <t>0.27%→0.10%</t>
+          <t>0.26%→0.09%</t>
         </is>
       </c>
       <c r="K93" s="13" t="inlineStr">
@@ -3789,11 +3789,11 @@
         <v>24</v>
       </c>
       <c r="C94" s="11" t="n">
-        <v>47923185</v>
+        <v>46463971</v>
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
-          <t>1.29%→1.48%</t>
+          <t>1.27%→1.46%</t>
         </is>
       </c>
       <c r="E94" s="13" t="inlineStr">
@@ -3810,11 +3810,11 @@
         <v>-19</v>
       </c>
       <c r="I94" s="15" t="n">
-        <v>-27967991</v>
+        <v>-28819182</v>
       </c>
       <c r="J94" s="16" t="inlineStr">
         <is>
-          <t>5.12%→4.98%</t>
+          <t>5.38%→5.23%</t>
         </is>
       </c>
       <c r="K94" s="13" t="inlineStr">
@@ -3833,11 +3833,11 @@
         <v>11</v>
       </c>
       <c r="C95" s="11" t="n">
-        <v>23900793</v>
+        <v>23372785</v>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>7.51%→7.56%</t>
+          <t>7.48%→7.54%</t>
         </is>
       </c>
       <c r="E95" s="13" t="inlineStr">
@@ -3854,11 +3854,11 @@
         <v>-15</v>
       </c>
       <c r="I95" s="15" t="n">
-        <v>-67967979</v>
+        <v>-67103958</v>
       </c>
       <c r="J95" s="16" t="inlineStr">
         <is>
-          <t>1.67%→1.38%</t>
+          <t>1.68%→1.39%</t>
         </is>
       </c>
       <c r="K95" s="13" t="inlineStr">
@@ -3877,11 +3877,11 @@
         <v>10</v>
       </c>
       <c r="C96" s="11" t="n">
-        <v>39871988</v>
+        <v>39295975</v>
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>1.03%→1.18%</t>
+          <t>1.03%→1.19%</t>
         </is>
       </c>
       <c r="E96" s="13" t="inlineStr">
@@ -3898,11 +3898,11 @@
         <v>-8</v>
       </c>
       <c r="I96" s="15" t="n">
-        <v>-55654383</v>
+        <v>-61183962</v>
       </c>
       <c r="J96" s="16" t="inlineStr">
         <is>
-          <t>1.42%→1.19%</t>
+          <t>1.59%→1.33%</t>
         </is>
       </c>
       <c r="K96" s="13" t="inlineStr">
@@ -3921,11 +3921,11 @@
         <v>7</v>
       </c>
       <c r="C97" s="11" t="n">
-        <v>36377589</v>
+        <v>38079976</v>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>1.23%→1.37%</t>
+          <t>1.32%→1.46%</t>
         </is>
       </c>
       <c r="E97" s="13" t="inlineStr">
@@ -3942,11 +3942,11 @@
         <v>-6</v>
       </c>
       <c r="I97" s="15" t="n">
-        <v>-45004786</v>
+        <v>-45119972</v>
       </c>
       <c r="J97" s="16" t="inlineStr">
         <is>
-          <t>2.79%→2.59%</t>
+          <t>2.85%→2.65%</t>
         </is>
       </c>
       <c r="K97" s="13" t="inlineStr">
@@ -3965,11 +3965,11 @@
         <v>7</v>
       </c>
       <c r="C98" s="11" t="n">
-        <v>48742385</v>
+        <v>49369569</v>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>2.19%→2.38%</t>
+          <t>2.26%→2.45%</t>
         </is>
       </c>
       <c r="E98" s="13" t="inlineStr">
@@ -3986,7 +3986,7 @@
         <v>-3</v>
       </c>
       <c r="I98" s="15" t="n">
-        <v>-7891198</v>
+        <v>-7823995</v>
       </c>
       <c r="J98" s="16" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>6</v>
       </c>
       <c r="C99" s="11" t="n">
-        <v>22348793</v>
+        <v>21427187</v>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
@@ -4037,11 +4037,11 @@
         <v>6</v>
       </c>
       <c r="C100" s="11" t="n">
-        <v>37055988</v>
+        <v>36710377</v>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>1.82%→1.96%</t>
+          <t>1.84%→1.98%</t>
         </is>
       </c>
       <c r="E100" s="13" t="inlineStr">
@@ -4073,925 +4073,2259 @@
       <c r="K102" s="19" t="n"/>
     </row>
     <row r="104" ht="19" customHeight="1">
-      <c r="A104" s="18" t="inlineStr">
-        <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B104" s="19" t="n"/>
-      <c r="C104" s="19" t="n"/>
-      <c r="D104" s="19" t="n"/>
-      <c r="E104" s="19" t="n"/>
-      <c r="F104" s="19" t="n"/>
-      <c r="G104" s="19" t="n"/>
-      <c r="H104" s="19" t="n"/>
-      <c r="I104" s="19" t="n"/>
-      <c r="J104" s="19" t="n"/>
-      <c r="K104" s="19" t="n"/>
-    </row>
-    <row r="106" ht="19" customHeight="1">
-      <c r="A106" s="3" t="inlineStr">
-        <is>
-          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 847억   ·   현금 3억(0.3%)      오늘 2026-10-26  vs  5일전 2026-10-19      매수 14종목  /  매도 19종목</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="n"/>
-      <c r="C106" s="4" t="n"/>
-      <c r="D106" s="4" t="n"/>
-      <c r="E106" s="4" t="n"/>
-      <c r="F106" s="4" t="n"/>
-      <c r="G106" s="4" t="n"/>
-      <c r="H106" s="4" t="n"/>
-      <c r="I106" s="4" t="n"/>
-      <c r="J106" s="4" t="n"/>
-      <c r="K106" s="4" t="n"/>
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,073억   ·   현금 58억(5.4%)      오늘 2026-10-26  vs  5일전 2026-10-19      매수 4종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="n"/>
+      <c r="C104" s="4" t="n"/>
+      <c r="D104" s="4" t="n"/>
+      <c r="E104" s="4" t="n"/>
+      <c r="F104" s="4" t="n"/>
+      <c r="G104" s="4" t="n"/>
+      <c r="H104" s="4" t="n"/>
+      <c r="I104" s="4" t="n"/>
+      <c r="J104" s="4" t="n"/>
+      <c r="K104" s="4" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="n"/>
+      <c r="C105" s="6" t="n"/>
+      <c r="D105" s="6" t="n"/>
+      <c r="E105" s="6" t="n"/>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H105" s="8" t="n"/>
+      <c r="I105" s="8" t="n"/>
+      <c r="J105" s="8" t="n"/>
+      <c r="K105" s="8" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E106" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G106" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H106" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I106" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K106" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="n"/>
-      <c r="C107" s="6" t="n"/>
-      <c r="D107" s="6" t="n"/>
-      <c r="E107" s="6" t="n"/>
-      <c r="G107" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H107" s="8" t="n"/>
-      <c r="I107" s="8" t="n"/>
-      <c r="J107" s="8" t="n"/>
-      <c r="K107" s="8" t="n"/>
+      <c r="A107" s="10" t="inlineStr">
+        <is>
+          <t>프로티나</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C107" s="11" t="n">
+        <v>270345835</v>
+      </c>
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t>2.67%→2.22%</t>
+        </is>
+      </c>
+      <c r="E107" s="13" t="inlineStr">
+        <is>
+          <t>22→25</t>
+        </is>
+      </c>
+      <c r="G107" s="14" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="H107" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I107" s="15" t="n">
+        <v>-565787064</v>
+      </c>
+      <c r="J107" s="16" t="inlineStr">
+        <is>
+          <t>7.63%→5.02%</t>
+        </is>
+      </c>
+      <c r="K107" s="13" t="inlineStr">
+        <is>
+          <t>40→36</t>
+        </is>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B108" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C108" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D108" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E108" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G108" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H108" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I108" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J108" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K108" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A108" s="10" t="inlineStr">
+        <is>
+          <t>HLB이노베이션</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C108" s="11" t="n">
+        <v>99054216</v>
+      </c>
+      <c r="D108" s="12" t="inlineStr">
+        <is>
+          <t>3.21%→2.44%</t>
+        </is>
+      </c>
+      <c r="E108" s="13" t="inlineStr">
+        <is>
+          <t>72→75</t>
+        </is>
+      </c>
+      <c r="G108" s="14" t="inlineStr">
+        <is>
+          <t>와이바이오로직스</t>
+        </is>
+      </c>
+      <c r="H108" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I108" s="15" t="n">
+        <v>-84951020</v>
+      </c>
+      <c r="J108" s="16" t="inlineStr">
+        <is>
+          <t>0.43%→0.23%</t>
+        </is>
+      </c>
+      <c r="K108" s="13" t="inlineStr">
+        <is>
+          <t>15→11</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="B109" s="11" t="n">
-        <v>832</v>
+        <v>3</v>
       </c>
       <c r="C109" s="11" t="n">
-        <v>1896584919</v>
+        <v>275323434</v>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>1.34%→3.87%</t>
+          <t>6.81%→5.24%</t>
         </is>
       </c>
       <c r="E109" s="13" t="inlineStr">
         <is>
-          <t>596→1,428</t>
+          <t>55→58</t>
         </is>
       </c>
       <c r="G109" s="14" t="inlineStr">
         <is>
-          <t>엠케이전자</t>
+          <t>오름테라퓨틱</t>
         </is>
       </c>
       <c r="H109" s="15" t="n">
-        <v>-431</v>
+        <v>-3</v>
       </c>
       <c r="I109" s="15" t="n">
-        <v>-1011996256</v>
+        <v>-101169696</v>
       </c>
       <c r="J109" s="16" t="inlineStr">
         <is>
-          <t>3.66%→1.97%</t>
+          <t>0.41%→0.20%</t>
         </is>
       </c>
       <c r="K109" s="13" t="inlineStr">
         <is>
-          <t>1,137→706</t>
+          <t>9→6</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B110" s="11" t="n">
-        <v>335</v>
+        <v>3</v>
       </c>
       <c r="C110" s="11" t="n">
-        <v>866587739</v>
+        <v>146216965</v>
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>4.89%→5.79%</t>
+          <t>6.77%→5.09%</t>
         </is>
       </c>
       <c r="E110" s="13" t="inlineStr">
         <is>
-          <t>1,550→1,885</t>
-        </is>
-      </c>
-      <c r="G110" s="14" t="inlineStr">
-        <is>
-          <t>코세스</t>
-        </is>
-      </c>
-      <c r="H110" s="15" t="n">
-        <v>-254</v>
-      </c>
-      <c r="I110" s="15" t="n">
-        <v>-1692477592</v>
-      </c>
-      <c r="J110" s="16" t="inlineStr">
-        <is>
-          <t>3.56%→2.98%</t>
-        </is>
-      </c>
-      <c r="K110" s="13" t="inlineStr">
-        <is>
-          <t>631→377</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="10" t="inlineStr">
-        <is>
-          <t>에프에스티  (신규)</t>
-        </is>
-      </c>
-      <c r="B111" s="11" t="n">
-        <v>256</v>
-      </c>
-      <c r="C111" s="11" t="n">
-        <v>1113689200</v>
-      </c>
-      <c r="D111" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→1.32%</t>
-        </is>
-      </c>
-      <c r="E111" s="13" t="inlineStr">
-        <is>
-          <t>0→256</t>
-        </is>
-      </c>
-      <c r="G111" s="14" t="inlineStr">
-        <is>
-          <t>저스템</t>
-        </is>
-      </c>
-      <c r="H111" s="15" t="n">
-        <v>-237</v>
-      </c>
-      <c r="I111" s="15" t="n">
-        <v>-539857366</v>
-      </c>
-      <c r="J111" s="16" t="inlineStr">
-        <is>
-          <t>2.79%→1.91%</t>
-        </is>
-      </c>
-      <c r="K111" s="13" t="inlineStr">
-        <is>
-          <t>942→705</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="10" t="inlineStr">
-        <is>
-          <t>아스플로</t>
-        </is>
-      </c>
-      <c r="B112" s="11" t="n">
-        <v>231</v>
-      </c>
-      <c r="C112" s="11" t="n">
-        <v>1224819310</v>
-      </c>
-      <c r="D112" s="12" t="inlineStr">
-        <is>
-          <t>1.84%→3.61%</t>
-        </is>
-      </c>
-      <c r="E112" s="13" t="inlineStr">
-        <is>
-          <t>343→574</t>
-        </is>
-      </c>
-      <c r="G112" s="14" t="inlineStr">
-        <is>
-          <t>SFA</t>
-        </is>
-      </c>
-      <c r="H112" s="15" t="n">
-        <v>-223</v>
-      </c>
-      <c r="I112" s="15" t="n">
-        <v>-945921060</v>
-      </c>
-      <c r="J112" s="16" t="inlineStr">
-        <is>
-          <t>1.67%→0.49%</t>
-        </is>
-      </c>
-      <c r="K112" s="13" t="inlineStr">
-        <is>
-          <t>320→97</t>
-        </is>
-      </c>
+          <t>103→106</t>
+        </is>
+      </c>
+      <c r="G110" s="17" t="n"/>
+      <c r="H110" s="17" t="n"/>
+      <c r="I110" s="17" t="n"/>
+      <c r="J110" s="17" t="n"/>
+      <c r="K110" s="17" t="n"/>
+    </row>
+    <row r="112" ht="19" customHeight="1">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 855억      오늘 2026-10-26  vs  5일전 2026-10-19      매수 14종목  /  매도 19종목</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="n"/>
+      <c r="C112" s="4" t="n"/>
+      <c r="D112" s="4" t="n"/>
+      <c r="E112" s="4" t="n"/>
+      <c r="F112" s="4" t="n"/>
+      <c r="G112" s="4" t="n"/>
+      <c r="H112" s="4" t="n"/>
+      <c r="I112" s="4" t="n"/>
+      <c r="J112" s="4" t="n"/>
+      <c r="K112" s="4" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="10" t="inlineStr">
-        <is>
-          <t>에스티아이</t>
-        </is>
-      </c>
-      <c r="B113" s="11" t="n">
-        <v>167</v>
-      </c>
-      <c r="C113" s="11" t="n">
-        <v>753002729</v>
-      </c>
-      <c r="D113" s="12" t="inlineStr">
-        <is>
-          <t>2.12%→2.85%</t>
-        </is>
-      </c>
-      <c r="E113" s="13" t="inlineStr">
-        <is>
-          <t>366→533</t>
-        </is>
-      </c>
-      <c r="G113" s="14" t="inlineStr">
-        <is>
-          <t>디케이티</t>
-        </is>
-      </c>
-      <c r="H113" s="15" t="n">
-        <v>-191</v>
-      </c>
-      <c r="I113" s="15" t="n">
-        <v>-826132003</v>
-      </c>
-      <c r="J113" s="16" t="inlineStr">
-        <is>
-          <t>4.57%→4.95%</t>
-        </is>
-      </c>
-      <c r="K113" s="13" t="inlineStr">
-        <is>
-          <t>1,155→964</t>
-        </is>
-      </c>
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="n"/>
+      <c r="C113" s="6" t="n"/>
+      <c r="D113" s="6" t="n"/>
+      <c r="E113" s="6" t="n"/>
+      <c r="G113" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H113" s="8" t="n"/>
+      <c r="I113" s="8" t="n"/>
+      <c r="J113" s="8" t="n"/>
+      <c r="K113" s="8" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="10" t="inlineStr">
-        <is>
-          <t>동진쎄미켐</t>
-        </is>
-      </c>
-      <c r="B114" s="11" t="n">
-        <v>95</v>
-      </c>
-      <c r="C114" s="11" t="n">
-        <v>620321277</v>
-      </c>
-      <c r="D114" s="12" t="inlineStr">
-        <is>
-          <t>2.15%→2.87%</t>
-        </is>
-      </c>
-      <c r="E114" s="13" t="inlineStr">
-        <is>
-          <t>275→370</t>
-        </is>
-      </c>
-      <c r="G114" s="14" t="inlineStr">
-        <is>
-          <t>태웅</t>
-        </is>
-      </c>
-      <c r="H114" s="15" t="n">
-        <v>-148</v>
-      </c>
-      <c r="I114" s="15" t="n">
-        <v>-625314575</v>
-      </c>
-      <c r="J114" s="16" t="inlineStr">
-        <is>
-          <t>1.01%→0.19%</t>
-        </is>
-      </c>
-      <c r="K114" s="13" t="inlineStr">
-        <is>
-          <t>186→38</t>
+      <c r="A114" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B114" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E114" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G114" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H114" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I114" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J114" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K114" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>RFHIC  (신규)</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="B115" s="11" t="n">
-        <v>89</v>
+        <v>832</v>
       </c>
       <c r="C115" s="11" t="n">
-        <v>674036808</v>
+        <v>1919298746</v>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.80%</t>
+          <t>1.34%→3.87%</t>
         </is>
       </c>
       <c r="E115" s="13" t="inlineStr">
         <is>
-          <t>0→89</t>
+          <t>596→1,428</t>
         </is>
       </c>
       <c r="G115" s="14" t="inlineStr">
         <is>
-          <t>네오셈</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="H115" s="15" t="n">
-        <v>-108</v>
+        <v>-431</v>
       </c>
       <c r="I115" s="15" t="n">
-        <v>-294527774</v>
+        <v>-1024116098</v>
       </c>
       <c r="J115" s="16" t="inlineStr">
         <is>
-          <t>2.24%→2.23%</t>
+          <t>3.66%→1.97%</t>
         </is>
       </c>
       <c r="K115" s="13" t="inlineStr">
         <is>
-          <t>797→689</t>
+          <t>1,137→706</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="B116" s="11" t="n">
-        <v>85</v>
+        <v>335</v>
       </c>
       <c r="C116" s="11" t="n">
-        <v>342099377</v>
+        <v>876966142</v>
       </c>
       <c r="D116" s="12" t="inlineStr">
         <is>
-          <t>1.46%→1.91%</t>
+          <t>4.89%→5.79%</t>
         </is>
       </c>
       <c r="E116" s="13" t="inlineStr">
         <is>
-          <t>314→399</t>
+          <t>1,550→1,885</t>
         </is>
       </c>
       <c r="G116" s="14" t="inlineStr">
         <is>
-          <t>싸이맥스  (편출)</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H116" s="15" t="n">
-        <v>-85</v>
+        <v>-254</v>
       </c>
       <c r="I116" s="15" t="n">
-        <v>-315838637</v>
+        <v>-1712746995</v>
       </c>
       <c r="J116" s="16" t="inlineStr">
         <is>
-          <t>0.36%→0.00%</t>
+          <t>3.56%→2.98%</t>
         </is>
       </c>
       <c r="K116" s="13" t="inlineStr">
         <is>
-          <t>85→0</t>
+          <t>631→377</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>에프에스티  (신규)</t>
         </is>
       </c>
       <c r="B117" s="11" t="n">
-        <v>51</v>
+        <v>256</v>
       </c>
       <c r="C117" s="11" t="n">
-        <v>477803528</v>
+        <v>1127026933</v>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>2.34%→2.97%</t>
+          <t>0.00%→1.32%</t>
         </is>
       </c>
       <c r="E117" s="13" t="inlineStr">
         <is>
-          <t>216→267</t>
+          <t>0→256</t>
         </is>
       </c>
       <c r="G117" s="14" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>저스템</t>
         </is>
       </c>
       <c r="H117" s="15" t="n">
-        <v>-62</v>
+        <v>-237</v>
       </c>
       <c r="I117" s="15" t="n">
-        <v>-637806171</v>
+        <v>-546322791</v>
       </c>
       <c r="J117" s="16" t="inlineStr">
         <is>
-          <t>4.71%→3.57%</t>
+          <t>2.79%→1.91%</t>
         </is>
       </c>
       <c r="K117" s="13" t="inlineStr">
         <is>
-          <t>354→292</t>
+          <t>942→705</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="B118" s="11" t="n">
-        <v>46</v>
+        <v>231</v>
       </c>
       <c r="C118" s="11" t="n">
-        <v>778186320</v>
+        <v>1239487957</v>
       </c>
       <c r="D118" s="12" t="inlineStr">
         <is>
-          <t>1.11%→1.93%</t>
+          <t>1.84%→3.61%</t>
         </is>
       </c>
       <c r="E118" s="13" t="inlineStr">
         <is>
-          <t>50→96</t>
+          <t>343→574</t>
         </is>
       </c>
       <c r="G118" s="14" t="inlineStr">
         <is>
-          <t>원익QnC  (편출)</t>
+          <t>SFA</t>
         </is>
       </c>
       <c r="H118" s="15" t="n">
-        <v>-57</v>
+        <v>-223</v>
       </c>
       <c r="I118" s="15" t="n">
-        <v>-266531904</v>
+        <v>-957249573</v>
       </c>
       <c r="J118" s="16" t="inlineStr">
         <is>
-          <t>0.30%→0.00%</t>
+          <t>1.67%→0.49%</t>
         </is>
       </c>
       <c r="K118" s="13" t="inlineStr">
         <is>
-          <t>57→0</t>
+          <t>320→97</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>미코</t>
+          <t>에스티아이</t>
         </is>
       </c>
       <c r="B119" s="11" t="n">
-        <v>41</v>
+        <v>167</v>
       </c>
       <c r="C119" s="11" t="n">
-        <v>153372745</v>
+        <v>762020820</v>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>4.97%→5.54%</t>
+          <t>2.12%→2.85%</t>
         </is>
       </c>
       <c r="E119" s="13" t="inlineStr">
         <is>
-          <t>1,206→1,247</t>
+          <t>366→533</t>
         </is>
       </c>
       <c r="G119" s="14" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>디케이티</t>
         </is>
       </c>
       <c r="H119" s="15" t="n">
-        <v>-49</v>
+        <v>-191</v>
       </c>
       <c r="I119" s="15" t="n">
-        <v>-536804607</v>
+        <v>-836025902</v>
       </c>
       <c r="J119" s="16" t="inlineStr">
         <is>
-          <t>1.12%→0.49%</t>
+          <t>4.57%→4.95%</t>
         </is>
       </c>
       <c r="K119" s="13" t="inlineStr">
         <is>
-          <t>87→38</t>
+          <t>1,155→964</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="B120" s="11" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="C120" s="11" t="n">
-        <v>217500722</v>
+        <v>627750351</v>
       </c>
       <c r="D120" s="12" t="inlineStr">
         <is>
-          <t>3.13%→3.29%</t>
+          <t>2.15%→2.87%</t>
         </is>
       </c>
       <c r="E120" s="13" t="inlineStr">
         <is>
-          <t>376→408</t>
+          <t>275→370</t>
         </is>
       </c>
       <c r="G120" s="14" t="inlineStr">
         <is>
-          <t>프로텍</t>
+          <t>태웅</t>
         </is>
       </c>
       <c r="H120" s="15" t="n">
-        <v>-41</v>
+        <v>-148</v>
       </c>
       <c r="I120" s="15" t="n">
-        <v>-410819852</v>
+        <v>-632803450</v>
       </c>
       <c r="J120" s="16" t="inlineStr">
         <is>
-          <t>0.92%→0.39%</t>
+          <t>1.01%→0.19%</t>
         </is>
       </c>
       <c r="K120" s="13" t="inlineStr">
         <is>
-          <t>74→33</t>
+          <t>186→38</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>RFHIC  (신규)</t>
         </is>
       </c>
       <c r="B121" s="11" t="n">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>235219415</v>
+        <v>682109189</v>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>1.78%→1.82%</t>
+          <t>0.00%→0.80%</t>
         </is>
       </c>
       <c r="E121" s="13" t="inlineStr">
         <is>
-          <t>166→196</t>
+          <t>0→89</t>
         </is>
       </c>
       <c r="G121" s="14" t="inlineStr">
         <is>
-          <t>씨엠티엑스  (편출)</t>
+          <t>네오셈</t>
         </is>
       </c>
       <c r="H121" s="15" t="n">
-        <v>-36</v>
+        <v>-108</v>
       </c>
       <c r="I121" s="15" t="n">
-        <v>-441280641</v>
+        <v>-298055089</v>
       </c>
       <c r="J121" s="16" t="inlineStr">
         <is>
-          <t>0.50%→0.00%</t>
+          <t>2.24%→2.23%</t>
         </is>
       </c>
       <c r="K121" s="13" t="inlineStr">
         <is>
-          <t>36→0</t>
+          <t>797→689</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
         <is>
+          <t>코미코</t>
+        </is>
+      </c>
+      <c r="B122" s="11" t="n">
+        <v>85</v>
+      </c>
+      <c r="C122" s="11" t="n">
+        <v>346196418</v>
+      </c>
+      <c r="D122" s="12" t="inlineStr">
+        <is>
+          <t>1.46%→1.91%</t>
+        </is>
+      </c>
+      <c r="E122" s="13" t="inlineStr">
+        <is>
+          <t>314→399</t>
+        </is>
+      </c>
+      <c r="G122" s="14" t="inlineStr">
+        <is>
+          <t>싸이맥스  (편출)</t>
+        </is>
+      </c>
+      <c r="H122" s="15" t="n">
+        <v>-85</v>
+      </c>
+      <c r="I122" s="15" t="n">
+        <v>-319621174</v>
+      </c>
+      <c r="J122" s="16" t="inlineStr">
+        <is>
+          <t>0.36%→0.00%</t>
+        </is>
+      </c>
+      <c r="K122" s="13" t="inlineStr">
+        <is>
+          <t>85→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="10" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="B123" s="11" t="n">
+        <v>51</v>
+      </c>
+      <c r="C123" s="11" t="n">
+        <v>483525786</v>
+      </c>
+      <c r="D123" s="12" t="inlineStr">
+        <is>
+          <t>2.34%→2.97%</t>
+        </is>
+      </c>
+      <c r="E123" s="13" t="inlineStr">
+        <is>
+          <t>216→267</t>
+        </is>
+      </c>
+      <c r="G123" s="14" t="inlineStr">
+        <is>
+          <t>리노공업</t>
+        </is>
+      </c>
+      <c r="H123" s="15" t="n">
+        <v>-62</v>
+      </c>
+      <c r="I123" s="15" t="n">
+        <v>-645444647</v>
+      </c>
+      <c r="J123" s="16" t="inlineStr">
+        <is>
+          <t>4.71%→3.57%</t>
+        </is>
+      </c>
+      <c r="K123" s="13" t="inlineStr">
+        <is>
+          <t>354→292</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="10" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="B124" s="11" t="n">
+        <v>46</v>
+      </c>
+      <c r="C124" s="11" t="n">
+        <v>787506014</v>
+      </c>
+      <c r="D124" s="12" t="inlineStr">
+        <is>
+          <t>1.11%→1.93%</t>
+        </is>
+      </c>
+      <c r="E124" s="13" t="inlineStr">
+        <is>
+          <t>50→96</t>
+        </is>
+      </c>
+      <c r="G124" s="14" t="inlineStr">
+        <is>
+          <t>원익QnC  (편출)</t>
+        </is>
+      </c>
+      <c r="H124" s="15" t="n">
+        <v>-57</v>
+      </c>
+      <c r="I124" s="15" t="n">
+        <v>-269723936</v>
+      </c>
+      <c r="J124" s="16" t="inlineStr">
+        <is>
+          <t>0.30%→0.00%</t>
+        </is>
+      </c>
+      <c r="K124" s="13" t="inlineStr">
+        <is>
+          <t>57→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="10" t="inlineStr">
+        <is>
+          <t>미코</t>
+        </is>
+      </c>
+      <c r="B125" s="11" t="n">
+        <v>41</v>
+      </c>
+      <c r="C125" s="11" t="n">
+        <v>155209563</v>
+      </c>
+      <c r="D125" s="12" t="inlineStr">
+        <is>
+          <t>4.97%→5.54%</t>
+        </is>
+      </c>
+      <c r="E125" s="13" t="inlineStr">
+        <is>
+          <t>1,206→1,247</t>
+        </is>
+      </c>
+      <c r="G125" s="14" t="inlineStr">
+        <is>
+          <t>제주반도체</t>
+        </is>
+      </c>
+      <c r="H125" s="15" t="n">
+        <v>-49</v>
+      </c>
+      <c r="I125" s="15" t="n">
+        <v>-543233471</v>
+      </c>
+      <c r="J125" s="16" t="inlineStr">
+        <is>
+          <t>1.12%→0.49%</t>
+        </is>
+      </c>
+      <c r="K125" s="13" t="inlineStr">
+        <is>
+          <t>87→38</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="10" t="inlineStr">
+        <is>
+          <t>이엔에프테크놀로지</t>
+        </is>
+      </c>
+      <c r="B126" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="C126" s="11" t="n">
+        <v>220105548</v>
+      </c>
+      <c r="D126" s="12" t="inlineStr">
+        <is>
+          <t>3.13%→3.29%</t>
+        </is>
+      </c>
+      <c r="E126" s="13" t="inlineStr">
+        <is>
+          <t>376→408</t>
+        </is>
+      </c>
+      <c r="G126" s="14" t="inlineStr">
+        <is>
+          <t>프로텍</t>
+        </is>
+      </c>
+      <c r="H126" s="15" t="n">
+        <v>-41</v>
+      </c>
+      <c r="I126" s="15" t="n">
+        <v>-415739902</v>
+      </c>
+      <c r="J126" s="16" t="inlineStr">
+        <is>
+          <t>0.92%→0.39%</t>
+        </is>
+      </c>
+      <c r="K126" s="13" t="inlineStr">
+        <is>
+          <t>74→33</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="10" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="B127" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="C127" s="11" t="n">
+        <v>238036444</v>
+      </c>
+      <c r="D127" s="12" t="inlineStr">
+        <is>
+          <t>1.78%→1.82%</t>
+        </is>
+      </c>
+      <c r="E127" s="13" t="inlineStr">
+        <is>
+          <t>166→196</t>
+        </is>
+      </c>
+      <c r="G127" s="14" t="inlineStr">
+        <is>
+          <t>씨엠티엑스  (편출)</t>
+        </is>
+      </c>
+      <c r="H127" s="15" t="n">
+        <v>-36</v>
+      </c>
+      <c r="I127" s="15" t="n">
+        <v>-446565494</v>
+      </c>
+      <c r="J127" s="16" t="inlineStr">
+        <is>
+          <t>0.50%→0.00%</t>
+        </is>
+      </c>
+      <c r="K127" s="13" t="inlineStr">
+        <is>
+          <t>36→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="10" t="inlineStr">
+        <is>
           <t>솔브레인</t>
         </is>
       </c>
-      <c r="B122" s="11" t="n">
+      <c r="B128" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C122" s="11" t="n">
-        <v>303605891</v>
-      </c>
-      <c r="D122" s="12" t="inlineStr">
+      <c r="C128" s="11" t="n">
+        <v>307241927</v>
+      </c>
+      <c r="D128" s="12" t="inlineStr">
         <is>
           <t>2.84%→3.06%</t>
         </is>
       </c>
-      <c r="E122" s="13" t="inlineStr">
+      <c r="E128" s="13" t="inlineStr">
         <is>
           <t>45→51</t>
         </is>
       </c>
-      <c r="G122" s="14" t="inlineStr">
+      <c r="G128" s="14" t="inlineStr">
         <is>
           <t>심텍</t>
         </is>
       </c>
-      <c r="H122" s="15" t="n">
+      <c r="H128" s="15" t="n">
         <v>-15</v>
       </c>
-      <c r="I122" s="15" t="n">
-        <v>-284317398</v>
-      </c>
-      <c r="J122" s="16" t="inlineStr">
+      <c r="I128" s="15" t="n">
+        <v>-287722432</v>
+      </c>
+      <c r="J128" s="16" t="inlineStr">
         <is>
           <t>6.16%→5.49%</t>
         </is>
       </c>
-      <c r="K122" s="13" t="inlineStr">
+      <c r="K128" s="13" t="inlineStr">
         <is>
           <t>259→244</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="17" t="n"/>
-      <c r="B123" s="17" t="n"/>
-      <c r="C123" s="17" t="n"/>
-      <c r="D123" s="17" t="n"/>
-      <c r="E123" s="17" t="n"/>
-      <c r="G123" s="14" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="17" t="n"/>
+      <c r="B129" s="17" t="n"/>
+      <c r="C129" s="17" t="n"/>
+      <c r="D129" s="17" t="n"/>
+      <c r="E129" s="17" t="n"/>
+      <c r="G129" s="14" t="inlineStr">
         <is>
           <t>파크시스템스</t>
         </is>
       </c>
-      <c r="H123" s="15" t="n">
+      <c r="H129" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="I123" s="15" t="n">
-        <v>-278221900</v>
-      </c>
-      <c r="J123" s="16" t="inlineStr">
+      <c r="I129" s="15" t="n">
+        <v>-281553933</v>
+      </c>
+      <c r="J129" s="16" t="inlineStr">
         <is>
           <t>1.96%→1.56%</t>
         </is>
       </c>
-      <c r="K123" s="13" t="inlineStr">
+      <c r="K129" s="13" t="inlineStr">
         <is>
           <t>40→33</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="17" t="n"/>
-      <c r="B124" s="17" t="n"/>
-      <c r="C124" s="17" t="n"/>
-      <c r="D124" s="17" t="n"/>
-      <c r="E124" s="17" t="n"/>
-      <c r="G124" s="14" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="17" t="n"/>
+      <c r="B130" s="17" t="n"/>
+      <c r="C130" s="17" t="n"/>
+      <c r="D130" s="17" t="n"/>
+      <c r="E130" s="17" t="n"/>
+      <c r="G130" s="14" t="inlineStr">
         <is>
           <t>티씨케이</t>
         </is>
       </c>
-      <c r="H124" s="15" t="n">
+      <c r="H130" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I124" s="15" t="n">
-        <v>-213926923</v>
-      </c>
-      <c r="J124" s="16" t="inlineStr">
+      <c r="I130" s="15" t="n">
+        <v>-216488949</v>
+      </c>
+      <c r="J130" s="16" t="inlineStr">
         <is>
           <t>0.59%→0.30%</t>
         </is>
       </c>
-      <c r="K124" s="13" t="inlineStr">
+      <c r="K130" s="13" t="inlineStr">
         <is>
           <t>13→7</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="17" t="n"/>
-      <c r="B125" s="17" t="n"/>
-      <c r="C125" s="17" t="n"/>
-      <c r="D125" s="17" t="n"/>
-      <c r="E125" s="17" t="n"/>
-      <c r="G125" s="14" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="17" t="n"/>
+      <c r="B131" s="17" t="n"/>
+      <c r="C131" s="17" t="n"/>
+      <c r="D131" s="17" t="n"/>
+      <c r="E131" s="17" t="n"/>
+      <c r="G131" s="14" t="inlineStr">
         <is>
           <t>피에스케이홀딩스</t>
         </is>
       </c>
-      <c r="H125" s="15" t="n">
+      <c r="H131" s="15" t="n">
         <v>-5</v>
       </c>
-      <c r="I125" s="15" t="n">
-        <v>-144705448</v>
-      </c>
-      <c r="J125" s="16" t="inlineStr">
+      <c r="I131" s="15" t="n">
+        <v>-146438465</v>
+      </c>
+      <c r="J131" s="16" t="inlineStr">
         <is>
           <t>2.58%→2.20%</t>
         </is>
       </c>
-      <c r="K125" s="13" t="inlineStr">
+      <c r="K131" s="13" t="inlineStr">
         <is>
           <t>69→64</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="17" t="n"/>
-      <c r="B126" s="17" t="n"/>
-      <c r="C126" s="17" t="n"/>
-      <c r="D126" s="17" t="n"/>
-      <c r="E126" s="17" t="n"/>
-      <c r="G126" s="14" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="17" t="n"/>
+      <c r="B132" s="17" t="n"/>
+      <c r="C132" s="17" t="n"/>
+      <c r="D132" s="17" t="n"/>
+      <c r="E132" s="17" t="n"/>
+      <c r="G132" s="14" t="inlineStr">
+        <is>
+          <t>티에스이</t>
+        </is>
+      </c>
+      <c r="H132" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I132" s="15" t="n">
+        <v>-173731959</v>
+      </c>
+      <c r="J132" s="16" t="inlineStr">
+        <is>
+          <t>2.57%→2.14%</t>
+        </is>
+      </c>
+      <c r="K132" s="13" t="inlineStr">
+        <is>
+          <t>46→42</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="17" t="n"/>
+      <c r="B133" s="17" t="n"/>
+      <c r="C133" s="17" t="n"/>
+      <c r="D133" s="17" t="n"/>
+      <c r="E133" s="17" t="n"/>
+      <c r="G133" s="14" t="inlineStr">
         <is>
           <t>이오테크닉스</t>
         </is>
       </c>
-      <c r="H126" s="15" t="n">
+      <c r="H133" s="15" t="n">
         <v>-4</v>
       </c>
-      <c r="I126" s="15" t="n">
-        <v>-269871903</v>
-      </c>
-      <c r="J126" s="16" t="inlineStr">
+      <c r="I133" s="15" t="n">
+        <v>-273103935</v>
+      </c>
+      <c r="J133" s="16" t="inlineStr">
         <is>
           <t>4.46%→3.93%</t>
         </is>
       </c>
-      <c r="K126" s="13" t="inlineStr">
+      <c r="K133" s="13" t="inlineStr">
         <is>
           <t>53→49</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="17" t="n"/>
-      <c r="B127" s="17" t="n"/>
-      <c r="C127" s="17" t="n"/>
-      <c r="D127" s="17" t="n"/>
-      <c r="E127" s="17" t="n"/>
-      <c r="G127" s="14" t="inlineStr">
-        <is>
-          <t>티에스이</t>
-        </is>
-      </c>
-      <c r="H127" s="15" t="n">
+    <row r="135" ht="19" customHeight="1">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 300억   ·   현금 4억(1.4%)      오늘 2026-10-26  vs  5일전 2026-10-19      매수 11종목  /  매도 22종목</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="n"/>
+      <c r="C135" s="4" t="n"/>
+      <c r="D135" s="4" t="n"/>
+      <c r="E135" s="4" t="n"/>
+      <c r="F135" s="4" t="n"/>
+      <c r="G135" s="4" t="n"/>
+      <c r="H135" s="4" t="n"/>
+      <c r="I135" s="4" t="n"/>
+      <c r="J135" s="4" t="n"/>
+      <c r="K135" s="4" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="n"/>
+      <c r="C136" s="6" t="n"/>
+      <c r="D136" s="6" t="n"/>
+      <c r="E136" s="6" t="n"/>
+      <c r="G136" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H136" s="8" t="n"/>
+      <c r="I136" s="8" t="n"/>
+      <c r="J136" s="8" t="n"/>
+      <c r="K136" s="8" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B137" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C137" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E137" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G137" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H137" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I137" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J137" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K137" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="10" t="inlineStr">
+        <is>
+          <t>파인엠텍  (신규)</t>
+        </is>
+      </c>
+      <c r="B138" s="11" t="n">
+        <v>77</v>
+      </c>
+      <c r="C138" s="11" t="n">
+        <v>364883836</v>
+      </c>
+      <c r="D138" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.23%</t>
+        </is>
+      </c>
+      <c r="E138" s="13" t="inlineStr">
+        <is>
+          <t>0→77</t>
+        </is>
+      </c>
+      <c r="G138" s="14" t="inlineStr">
+        <is>
+          <t>동국산업</t>
+        </is>
+      </c>
+      <c r="H138" s="15" t="n">
+        <v>-135</v>
+      </c>
+      <c r="I138" s="15" t="n">
+        <v>-211713800</v>
+      </c>
+      <c r="J138" s="16" t="inlineStr">
+        <is>
+          <t>1.63%→0.90%</t>
+        </is>
+      </c>
+      <c r="K138" s="13" t="inlineStr">
+        <is>
+          <t>305→170</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="10" t="inlineStr">
+        <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="B139" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="C139" s="11" t="n">
+        <v>1153110271</v>
+      </c>
+      <c r="D139" s="12" t="inlineStr">
+        <is>
+          <t>3.76%→7.62%</t>
+        </is>
+      </c>
+      <c r="E139" s="13" t="inlineStr">
+        <is>
+          <t>65→133</t>
+        </is>
+      </c>
+      <c r="G139" s="14" t="inlineStr">
+        <is>
+          <t>에이팩트</t>
+        </is>
+      </c>
+      <c r="H139" s="15" t="n">
+        <v>-62</v>
+      </c>
+      <c r="I139" s="15" t="n">
+        <v>-245318558</v>
+      </c>
+      <c r="J139" s="16" t="inlineStr">
+        <is>
+          <t>3.24%→2.38%</t>
+        </is>
+      </c>
+      <c r="K139" s="13" t="inlineStr">
+        <is>
+          <t>240→178</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="10" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="B140" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C140" s="11" t="n">
+        <v>282200066</v>
+      </c>
+      <c r="D140" s="12" t="inlineStr">
+        <is>
+          <t>3.37%→4.29%</t>
+        </is>
+      </c>
+      <c r="E140" s="13" t="inlineStr">
+        <is>
+          <t>70→90</t>
+        </is>
+      </c>
+      <c r="G140" s="14" t="inlineStr">
+        <is>
+          <t>덕산하이메탈</t>
+        </is>
+      </c>
+      <c r="H140" s="15" t="n">
+        <v>-50</v>
+      </c>
+      <c r="I140" s="15" t="n">
+        <v>-238000056</v>
+      </c>
+      <c r="J140" s="16" t="inlineStr">
+        <is>
+          <t>1.46%→0.64%</t>
+        </is>
+      </c>
+      <c r="K140" s="13" t="inlineStr">
+        <is>
+          <t>90→40</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="10" t="inlineStr">
+        <is>
+          <t>지투지바이오</t>
+        </is>
+      </c>
+      <c r="B141" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C141" s="11" t="n">
+        <v>422450099</v>
+      </c>
+      <c r="D141" s="12" t="inlineStr">
+        <is>
+          <t>0.65%→2.07%</t>
+        </is>
+      </c>
+      <c r="E141" s="13" t="inlineStr">
+        <is>
+          <t>9→29</t>
+        </is>
+      </c>
+      <c r="G141" s="14" t="inlineStr">
+        <is>
+          <t>피엠티</t>
+        </is>
+      </c>
+      <c r="H141" s="15" t="n">
+        <v>-50</v>
+      </c>
+      <c r="I141" s="15" t="n">
+        <v>-71293767</v>
+      </c>
+      <c r="J141" s="16" t="inlineStr">
+        <is>
+          <t>0.26%→0.01%</t>
+        </is>
+      </c>
+      <c r="K141" s="13" t="inlineStr">
+        <is>
+          <t>53→3</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="10" t="inlineStr">
+        <is>
+          <t>프로티나  (신규)</t>
+        </is>
+      </c>
+      <c r="B142" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="C142" s="11" t="n">
+        <v>350858833</v>
+      </c>
+      <c r="D142" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.19%</t>
+        </is>
+      </c>
+      <c r="E142" s="13" t="inlineStr">
+        <is>
+          <t>0→19</t>
+        </is>
+      </c>
+      <c r="G142" s="14" t="inlineStr">
+        <is>
+          <t>글로벌텍스프리</t>
+        </is>
+      </c>
+      <c r="H142" s="15" t="n">
+        <v>-46</v>
+      </c>
+      <c r="I142" s="15" t="n">
+        <v>-105374525</v>
+      </c>
+      <c r="J142" s="16" t="inlineStr">
+        <is>
+          <t>1.04%→0.67%</t>
+        </is>
+      </c>
+      <c r="K142" s="13" t="inlineStr">
+        <is>
+          <t>133→87</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="10" t="inlineStr">
+        <is>
+          <t>태성</t>
+        </is>
+      </c>
+      <c r="B143" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="C143" s="11" t="n">
+        <v>305830072</v>
+      </c>
+      <c r="D143" s="12" t="inlineStr">
+        <is>
+          <t>0.97%→1.99%</t>
+        </is>
+      </c>
+      <c r="E143" s="13" t="inlineStr">
+        <is>
+          <t>13→27</t>
+        </is>
+      </c>
+      <c r="G143" s="14" t="inlineStr">
+        <is>
+          <t>HT로보틱스</t>
+        </is>
+      </c>
+      <c r="H143" s="15" t="n">
+        <v>-45</v>
+      </c>
+      <c r="I143" s="15" t="n">
+        <v>-176141291</v>
+      </c>
+      <c r="J143" s="16" t="inlineStr">
+        <is>
+          <t>0.64%→0.04%</t>
+        </is>
+      </c>
+      <c r="K143" s="13" t="inlineStr">
+        <is>
+          <t>48→3</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="10" t="inlineStr">
+        <is>
+          <t>선익시스템  (신규)</t>
+        </is>
+      </c>
+      <c r="B144" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C144" s="11" t="n">
+        <v>325125076</v>
+      </c>
+      <c r="D144" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.10%</t>
+        </is>
+      </c>
+      <c r="E144" s="13" t="inlineStr">
+        <is>
+          <t>0→9</t>
+        </is>
+      </c>
+      <c r="G144" s="14" t="inlineStr">
+        <is>
+          <t>LS머트리얼즈  (편출)</t>
+        </is>
+      </c>
+      <c r="H144" s="15" t="n">
+        <v>-42</v>
+      </c>
+      <c r="I144" s="15" t="n">
+        <v>-230979054</v>
+      </c>
+      <c r="J144" s="16" t="inlineStr">
+        <is>
+          <t>0.79%→0.00%</t>
+        </is>
+      </c>
+      <c r="K144" s="13" t="inlineStr">
+        <is>
+          <t>42→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="10" t="inlineStr">
+        <is>
+          <t>알지노믹스</t>
+        </is>
+      </c>
+      <c r="B145" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C145" s="11" t="n">
+        <v>89887521</v>
+      </c>
+      <c r="D145" s="12" t="inlineStr">
+        <is>
+          <t>0.72%→1.01%</t>
+        </is>
+      </c>
+      <c r="E145" s="13" t="inlineStr">
+        <is>
+          <t>21→30</t>
+        </is>
+      </c>
+      <c r="G145" s="14" t="inlineStr">
+        <is>
+          <t>피노</t>
+        </is>
+      </c>
+      <c r="H145" s="15" t="n">
+        <v>-39</v>
+      </c>
+      <c r="I145" s="15" t="n">
+        <v>-114036027</v>
+      </c>
+      <c r="J145" s="16" t="inlineStr">
+        <is>
+          <t>3.10%→2.69%</t>
+        </is>
+      </c>
+      <c r="K145" s="13" t="inlineStr">
+        <is>
+          <t>311→272</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="10" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="B146" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C146" s="11" t="n">
+        <v>307317572</v>
+      </c>
+      <c r="D146" s="12" t="inlineStr">
+        <is>
+          <t>2.69%→3.71%</t>
+        </is>
+      </c>
+      <c r="E146" s="13" t="inlineStr">
+        <is>
+          <t>18→25</t>
+        </is>
+      </c>
+      <c r="G146" s="14" t="inlineStr">
+        <is>
+          <t>성호전자  (편출)</t>
+        </is>
+      </c>
+      <c r="H146" s="15" t="n">
+        <v>-27</v>
+      </c>
+      <c r="I146" s="15" t="n">
+        <v>-302366321</v>
+      </c>
+      <c r="J146" s="16" t="inlineStr">
+        <is>
+          <t>1.03%→0.00%</t>
+        </is>
+      </c>
+      <c r="K146" s="13" t="inlineStr">
+        <is>
+          <t>27→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="10" t="inlineStr">
+        <is>
+          <t>지엔씨에너지</t>
+        </is>
+      </c>
+      <c r="B147" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C147" s="11" t="n">
+        <v>120636278</v>
+      </c>
+      <c r="D147" s="12" t="inlineStr">
+        <is>
+          <t>0.53%→0.93%</t>
+        </is>
+      </c>
+      <c r="E147" s="13" t="inlineStr">
+        <is>
+          <t>9→16</t>
+        </is>
+      </c>
+      <c r="G147" s="14" t="inlineStr">
+        <is>
+          <t>큐리언트  (편출)</t>
+        </is>
+      </c>
+      <c r="H147" s="15" t="n">
+        <v>-24</v>
+      </c>
+      <c r="I147" s="15" t="n">
+        <v>-198594047</v>
+      </c>
+      <c r="J147" s="16" t="inlineStr">
+        <is>
+          <t>0.68%→0.00%</t>
+        </is>
+      </c>
+      <c r="K147" s="13" t="inlineStr">
+        <is>
+          <t>24→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="10" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="B148" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C148" s="11" t="n">
+        <v>144712534</v>
+      </c>
+      <c r="D148" s="12" t="inlineStr">
+        <is>
+          <t>5.10%→5.54%</t>
+        </is>
+      </c>
+      <c r="E148" s="13" t="inlineStr">
+        <is>
+          <t>31→34</t>
+        </is>
+      </c>
+      <c r="G148" s="14" t="inlineStr">
+        <is>
+          <t>엔알비  (편출)</t>
+        </is>
+      </c>
+      <c r="H148" s="15" t="n">
+        <v>-23</v>
+      </c>
+      <c r="I148" s="15" t="n">
+        <v>-87975021</v>
+      </c>
+      <c r="J148" s="16" t="inlineStr">
+        <is>
+          <t>0.30%→0.00%</t>
+        </is>
+      </c>
+      <c r="K148" s="13" t="inlineStr">
+        <is>
+          <t>23→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="17" t="n"/>
+      <c r="B149" s="17" t="n"/>
+      <c r="C149" s="17" t="n"/>
+      <c r="D149" s="17" t="n"/>
+      <c r="E149" s="17" t="n"/>
+      <c r="G149" s="14" t="inlineStr">
+        <is>
+          <t>네오티스</t>
+        </is>
+      </c>
+      <c r="H149" s="15" t="n">
+        <v>-21</v>
+      </c>
+      <c r="I149" s="15" t="n">
+        <v>-181177543</v>
+      </c>
+      <c r="J149" s="16" t="inlineStr">
+        <is>
+          <t>1.29%→0.67%</t>
+        </is>
+      </c>
+      <c r="K149" s="13" t="inlineStr">
+        <is>
+          <t>44→23</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="17" t="n"/>
+      <c r="B150" s="17" t="n"/>
+      <c r="C150" s="17" t="n"/>
+      <c r="D150" s="17" t="n"/>
+      <c r="E150" s="17" t="n"/>
+      <c r="G150" s="14" t="inlineStr">
+        <is>
+          <t>오킨스전자</t>
+        </is>
+      </c>
+      <c r="H150" s="15" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I150" s="15" t="n">
+        <v>-127500030</v>
+      </c>
+      <c r="J150" s="16" t="inlineStr">
+        <is>
+          <t>1.27%→0.83%</t>
+        </is>
+      </c>
+      <c r="K150" s="13" t="inlineStr">
+        <is>
+          <t>35→23</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="17" t="n"/>
+      <c r="B151" s="17" t="n"/>
+      <c r="C151" s="17" t="n"/>
+      <c r="D151" s="17" t="n"/>
+      <c r="E151" s="17" t="n"/>
+      <c r="G151" s="14" t="inlineStr">
+        <is>
+          <t>네패스</t>
+        </is>
+      </c>
+      <c r="H151" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I151" s="15" t="n">
+        <v>-108927526</v>
+      </c>
+      <c r="J151" s="16" t="inlineStr">
+        <is>
+          <t>0.91%→0.54%</t>
+        </is>
+      </c>
+      <c r="K151" s="13" t="inlineStr">
+        <is>
+          <t>27→16</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="17" t="n"/>
+      <c r="B152" s="17" t="n"/>
+      <c r="C152" s="17" t="n"/>
+      <c r="D152" s="17" t="n"/>
+      <c r="E152" s="17" t="n"/>
+      <c r="G152" s="14" t="inlineStr">
+        <is>
+          <t>HLB이노베이션</t>
+        </is>
+      </c>
+      <c r="H152" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I152" s="15" t="n">
+        <v>-74426018</v>
+      </c>
+      <c r="J152" s="16" t="inlineStr">
+        <is>
+          <t>0.92%→0.66%</t>
+        </is>
+      </c>
+      <c r="K152" s="13" t="inlineStr">
+        <is>
+          <t>40→29</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="17" t="n"/>
+      <c r="B153" s="17" t="n"/>
+      <c r="C153" s="17" t="n"/>
+      <c r="D153" s="17" t="n"/>
+      <c r="E153" s="17" t="n"/>
+      <c r="G153" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="H153" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I153" s="15" t="n">
+        <v>-549312629</v>
+      </c>
+      <c r="J153" s="16" t="inlineStr">
+        <is>
+          <t>2.89%→1.01%</t>
+        </is>
+      </c>
+      <c r="K153" s="13" t="inlineStr">
+        <is>
+          <t>17→6</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="17" t="n"/>
+      <c r="B154" s="17" t="n"/>
+      <c r="C154" s="17" t="n"/>
+      <c r="D154" s="17" t="n"/>
+      <c r="E154" s="17" t="n"/>
+      <c r="G154" s="14" t="inlineStr">
+        <is>
+          <t>덕산테코피아</t>
+        </is>
+      </c>
+      <c r="H154" s="15" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I154" s="15" t="n">
+        <v>-37676259</v>
+      </c>
+      <c r="J154" s="16" t="inlineStr">
+        <is>
+          <t>0.33%→0.20%</t>
+        </is>
+      </c>
+      <c r="K154" s="13" t="inlineStr">
+        <is>
+          <t>23→14</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="17" t="n"/>
+      <c r="B155" s="17" t="n"/>
+      <c r="C155" s="17" t="n"/>
+      <c r="D155" s="17" t="n"/>
+      <c r="E155" s="17" t="n"/>
+      <c r="G155" s="14" t="inlineStr">
+        <is>
+          <t>오이솔루션</t>
+        </is>
+      </c>
+      <c r="H155" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I155" s="15" t="n">
+        <v>-75267518</v>
+      </c>
+      <c r="J155" s="16" t="inlineStr">
+        <is>
+          <t>1.03%→0.76%</t>
+        </is>
+      </c>
+      <c r="K155" s="13" t="inlineStr">
+        <is>
+          <t>28→21</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="17" t="n"/>
+      <c r="B156" s="17" t="n"/>
+      <c r="C156" s="17" t="n"/>
+      <c r="D156" s="17" t="n"/>
+      <c r="E156" s="17" t="n"/>
+      <c r="G156" s="14" t="inlineStr">
+        <is>
+          <t>인텔리안테크</t>
+        </is>
+      </c>
+      <c r="H156" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I156" s="15" t="n">
+        <v>-113050027</v>
+      </c>
+      <c r="J156" s="16" t="inlineStr">
+        <is>
+          <t>0.77%→0.38%</t>
+        </is>
+      </c>
+      <c r="K156" s="13" t="inlineStr">
+        <is>
+          <t>10→5</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="17" t="n"/>
+      <c r="B157" s="17" t="n"/>
+      <c r="C157" s="17" t="n"/>
+      <c r="D157" s="17" t="n"/>
+      <c r="E157" s="17" t="n"/>
+      <c r="G157" s="14" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="H157" s="15" t="n">
         <v>-4</v>
       </c>
-      <c r="I127" s="15" t="n">
-        <v>-171675938</v>
-      </c>
-      <c r="J127" s="16" t="inlineStr">
-        <is>
-          <t>2.57%→2.14%</t>
-        </is>
-      </c>
-      <c r="K127" s="13" t="inlineStr">
-        <is>
-          <t>46→42</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="19" customHeight="1">
-      <c r="A129" s="18" t="inlineStr">
-        <is>
-          <t>■ TIGER 코스닥액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B129" s="19" t="n"/>
-      <c r="C129" s="19" t="n"/>
-      <c r="D129" s="19" t="n"/>
-      <c r="E129" s="19" t="n"/>
-      <c r="F129" s="19" t="n"/>
-      <c r="G129" s="19" t="n"/>
-      <c r="H129" s="19" t="n"/>
-      <c r="I129" s="19" t="n"/>
-      <c r="J129" s="19" t="n"/>
-      <c r="K129" s="19" t="n"/>
-    </row>
-    <row r="131" ht="19" customHeight="1">
-      <c r="A131" s="18" t="inlineStr">
-        <is>
-          <t>■ MIDAS 코스닥액티브  (마이다스)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B131" s="19" t="n"/>
-      <c r="C131" s="19" t="n"/>
-      <c r="D131" s="19" t="n"/>
-      <c r="E131" s="19" t="n"/>
-      <c r="F131" s="19" t="n"/>
-      <c r="G131" s="19" t="n"/>
-      <c r="H131" s="19" t="n"/>
-      <c r="I131" s="19" t="n"/>
-      <c r="J131" s="19" t="n"/>
-      <c r="K131" s="19" t="n"/>
+      <c r="I157" s="15" t="n">
+        <v>-172210041</v>
+      </c>
+      <c r="J157" s="16" t="inlineStr">
+        <is>
+          <t>1.03%→0.44%</t>
+        </is>
+      </c>
+      <c r="K157" s="13" t="inlineStr">
+        <is>
+          <t>7→3</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="17" t="n"/>
+      <c r="B158" s="17" t="n"/>
+      <c r="C158" s="17" t="n"/>
+      <c r="D158" s="17" t="n"/>
+      <c r="E158" s="17" t="n"/>
+      <c r="G158" s="14" t="inlineStr">
+        <is>
+          <t>펌텍코리아</t>
+        </is>
+      </c>
+      <c r="H158" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I158" s="15" t="n">
+        <v>-118490028</v>
+      </c>
+      <c r="J158" s="16" t="inlineStr">
+        <is>
+          <t>3.64%→3.20%</t>
+        </is>
+      </c>
+      <c r="K158" s="13" t="inlineStr">
+        <is>
+          <t>36→32</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="17" t="n"/>
+      <c r="B159" s="17" t="n"/>
+      <c r="C159" s="17" t="n"/>
+      <c r="D159" s="17" t="n"/>
+      <c r="E159" s="17" t="n"/>
+      <c r="G159" s="14" t="inlineStr">
+        <is>
+          <t>한라IMS</t>
+        </is>
+      </c>
+      <c r="H159" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I159" s="15" t="n">
+        <v>-17901004</v>
+      </c>
+      <c r="J159" s="16" t="inlineStr">
+        <is>
+          <t>0.35%→0.28%</t>
+        </is>
+      </c>
+      <c r="K159" s="13" t="inlineStr">
+        <is>
+          <t>17→14</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="19" customHeight="1">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 56억   ·   현금 1억(1.7%)      오늘 2026-10-26  vs  5일전 2026-10-19      매수 4종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="n"/>
+      <c r="C161" s="4" t="n"/>
+      <c r="D161" s="4" t="n"/>
+      <c r="E161" s="4" t="n"/>
+      <c r="F161" s="4" t="n"/>
+      <c r="G161" s="4" t="n"/>
+      <c r="H161" s="4" t="n"/>
+      <c r="I161" s="4" t="n"/>
+      <c r="J161" s="4" t="n"/>
+      <c r="K161" s="4" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B162" s="6" t="n"/>
+      <c r="C162" s="6" t="n"/>
+      <c r="D162" s="6" t="n"/>
+      <c r="E162" s="6" t="n"/>
+      <c r="G162" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H162" s="8" t="n"/>
+      <c r="I162" s="8" t="n"/>
+      <c r="J162" s="8" t="n"/>
+      <c r="K162" s="8" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B163" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C163" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D163" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E163" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G163" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H163" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I163" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J163" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K163" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="10" t="inlineStr">
+        <is>
+          <t>큐리언트  (신규)</t>
+        </is>
+      </c>
+      <c r="B164" s="11" t="n">
+        <v>176</v>
+      </c>
+      <c r="C164" s="11" t="n">
+        <v>27413760</v>
+      </c>
+      <c r="D164" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.50%</t>
+        </is>
+      </c>
+      <c r="E164" s="13" t="inlineStr">
+        <is>
+          <t>0→176</t>
+        </is>
+      </c>
+      <c r="G164" s="14" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="H164" s="15" t="n">
+        <v>-98</v>
+      </c>
+      <c r="I164" s="15" t="n">
+        <v>-26969600</v>
+      </c>
+      <c r="J164" s="16" t="inlineStr">
+        <is>
+          <t>3.44%→2.94%</t>
+        </is>
+      </c>
+      <c r="K164" s="13" t="inlineStr">
+        <is>
+          <t>683→585</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="10" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="B165" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="C165" s="11" t="n">
+        <v>21033600</v>
+      </c>
+      <c r="D165" s="12" t="inlineStr">
+        <is>
+          <t>3.08%→3.46%</t>
+        </is>
+      </c>
+      <c r="E165" s="13" t="inlineStr">
+        <is>
+          <t>449→505</t>
+        </is>
+      </c>
+      <c r="G165" s="14" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="H165" s="15" t="n">
+        <v>-28</v>
+      </c>
+      <c r="I165" s="15" t="n">
+        <v>-24684800</v>
+      </c>
+      <c r="J165" s="16" t="inlineStr">
+        <is>
+          <t>4.46%→4.00%</t>
+        </is>
+      </c>
+      <c r="K165" s="13" t="inlineStr">
+        <is>
+          <t>277→249</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="10" t="inlineStr">
+        <is>
+          <t>대주전자재료</t>
+        </is>
+      </c>
+      <c r="B166" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C166" s="11" t="n">
+        <v>9216000</v>
+      </c>
+      <c r="D166" s="12" t="inlineStr">
+        <is>
+          <t>2.49%→2.65%</t>
+        </is>
+      </c>
+      <c r="E166" s="13" t="inlineStr">
+        <is>
+          <t>177→189</t>
+        </is>
+      </c>
+      <c r="G166" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="H166" s="15" t="n">
+        <v>-19</v>
+      </c>
+      <c r="I166" s="15" t="n">
+        <v>-26341600</v>
+      </c>
+      <c r="J166" s="16" t="inlineStr">
+        <is>
+          <t>5.12%→4.63%</t>
+        </is>
+      </c>
+      <c r="K166" s="13" t="inlineStr">
+        <is>
+          <t>202→183</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="10" t="inlineStr">
+        <is>
+          <t>이오테크닉스</t>
+        </is>
+      </c>
+      <c r="B167" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C167" s="11" t="n">
+        <v>35552000</v>
+      </c>
+      <c r="D167" s="12" t="inlineStr">
+        <is>
+          <t>5.97%→6.60%</t>
+        </is>
+      </c>
+      <c r="E167" s="13" t="inlineStr">
+        <is>
+          <t>101→112</t>
+        </is>
+      </c>
+      <c r="G167" s="17" t="n"/>
+      <c r="H167" s="17" t="n"/>
+      <c r="I167" s="17" t="n"/>
+      <c r="J167" s="17" t="n"/>
+      <c r="K167" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="30">
+    <mergeCell ref="G105:K105"/>
     <mergeCell ref="A24:K24"/>
-    <mergeCell ref="A107:E107"/>
     <mergeCell ref="A45:E45"/>
-    <mergeCell ref="G107:K107"/>
+    <mergeCell ref="G136:K136"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A79:K79"/>
+    <mergeCell ref="A162:E162"/>
     <mergeCell ref="A88:K88"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A89:E89"/>
+    <mergeCell ref="G162:K162"/>
     <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A136:E136"/>
+    <mergeCell ref="A105:E105"/>
     <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A113:E113"/>
     <mergeCell ref="A104:K104"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="G89:K89"/>
-    <mergeCell ref="A129:K129"/>
     <mergeCell ref="G80:K80"/>
     <mergeCell ref="G45:K45"/>
     <mergeCell ref="G4:K4"/>
-    <mergeCell ref="A106:K106"/>
+    <mergeCell ref="A135:K135"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A131:K131"/>
+    <mergeCell ref="G113:K113"/>
+    <mergeCell ref="A112:K112"/>
     <mergeCell ref="G25:K25"/>
+    <mergeCell ref="A161:K161"/>
     <mergeCell ref="A44:K44"/>
     <mergeCell ref="A102:K102"/>
   </mergeCells>

--- a/reports/pdf_rolling5_20261026.xlsx
+++ b/reports/pdf_rolling5_20261026.xlsx
@@ -1186,23 +1186,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>403166514</v>
+        <v>2838864800</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>1.43%→1.44%</t>
+          <t>1.45%→2.03%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>173→185</t>
+          <t>25→37</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1258,23 +1258,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>2838864800</v>
+        <v>403166514</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>1.45%→2.03%</t>
+          <t>1.43%→1.44%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>25→37</t>
+          <t>173→185</t>
         </is>
       </c>
       <c r="G20" s="17" t="n"/>
@@ -2228,23 +2228,23 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>코세스  (신규)</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="B50" s="11" t="n">
         <v>250</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>6583503591</v>
+        <v>6690753650</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>0.00%→3.08%</t>
+          <t>2.91%→6.27%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>0→250</t>
+          <t>250→500</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
@@ -2272,23 +2272,23 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>코세스  (신규)</t>
         </is>
       </c>
       <c r="B51" s="11" t="n">
         <v>250</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>6690753650</v>
+        <v>6583503591</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>2.91%→6.27%</t>
+          <t>0.00%→3.08%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>250→500</t>
+          <t>0→250</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
@@ -2469,23 +2469,23 @@
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
         <v>-105</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-5391542941</v>
+        <v>-7636864166</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>4.01%→1.80%</t>
+          <t>4.63%→0.85%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>180→75</t>
+          <t>130→25</t>
         </is>
       </c>
     </row>
@@ -2513,23 +2513,23 @@
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-105</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-7636864166</v>
+        <v>-5391542941</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>4.63%→0.85%</t>
+          <t>4.01%→1.80%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>130→25</t>
+          <t>180→75</t>
         </is>
       </c>
     </row>
@@ -2777,23 +2777,23 @@
       </c>
       <c r="G62" s="14" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H62" s="15" t="n">
         <v>-49</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-2121505157</v>
+        <v>-3279277789</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>1.91%→1.01%</t>
+          <t>2.86%→1.25%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
         <is>
-          <t>99→50</t>
+          <t>89→40</t>
         </is>
       </c>
     </row>
@@ -2821,46 +2821,46 @@
       </c>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="H63" s="15" t="n">
         <v>-49</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-3279277789</v>
+        <v>-2121505157</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>2.86%→1.25%</t>
+          <t>1.91%→1.01%</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
         <is>
-          <t>89→40</t>
+          <t>99→50</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B64" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>1715670936</v>
+        <v>1002870547</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>5.87%→6.43%</t>
+          <t>0.47%→0.91%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>105→120</t>
+          <t>14→29</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
@@ -2888,23 +2888,23 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B65" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>1002870547</v>
+        <v>1715670936</v>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>0.47%→0.91%</t>
+          <t>5.87%→6.43%</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
-          <t>14→29</t>
+          <t>105→120</t>
         </is>
       </c>
       <c r="G65" s="14" t="inlineStr">
@@ -3205,23 +3205,23 @@
       <c r="E75" s="17" t="n"/>
       <c r="G75" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>보로노이  (편출)</t>
         </is>
       </c>
       <c r="H75" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I75" s="15" t="n">
-        <v>-1861201015</v>
+        <v>-650496355</v>
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
-          <t>2.67%→2.07%</t>
+          <t>0.28%→0.00%</t>
         </is>
       </c>
       <c r="K75" s="13" t="inlineStr">
         <is>
-          <t>27→19</t>
+          <t>8→0</t>
         </is>
       </c>
     </row>
@@ -3233,23 +3233,23 @@
       <c r="E76" s="17" t="n"/>
       <c r="G76" s="14" t="inlineStr">
         <is>
-          <t>보로노이  (편출)</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H76" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I76" s="15" t="n">
-        <v>-650496355</v>
+        <v>-1861201015</v>
       </c>
       <c r="J76" s="16" t="inlineStr">
         <is>
-          <t>0.28%→0.00%</t>
+          <t>2.67%→2.07%</t>
         </is>
       </c>
       <c r="K76" s="13" t="inlineStr">
         <is>
-          <t>8→0</t>
+          <t>27→19</t>
         </is>
       </c>
     </row>
@@ -4002,23 +4002,23 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>나노신소재</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B99" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C99" s="11" t="n">
-        <v>21427187</v>
+        <v>36710377</v>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>0.12%→0.21%</t>
+          <t>1.84%→1.98%</t>
         </is>
       </c>
       <c r="E99" s="13" t="inlineStr">
         <is>
-          <t>8→14</t>
+          <t>72→78</t>
         </is>
       </c>
       <c r="G99" s="17" t="n"/>
@@ -4030,23 +4030,23 @@
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>나노신소재</t>
         </is>
       </c>
       <c r="B100" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C100" s="11" t="n">
-        <v>36710377</v>
+        <v>21427187</v>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>1.84%→1.98%</t>
+          <t>0.12%→0.21%</t>
         </is>
       </c>
       <c r="E100" s="13" t="inlineStr">
         <is>
-          <t>72→78</t>
+          <t>8→14</t>
         </is>
       </c>
       <c r="G100" s="17" t="n"/>
@@ -4075,7 +4075,7 @@
     <row r="104" ht="19" customHeight="1">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,073억   ·   현금 58억(5.4%)      오늘 2026-10-26  vs  5일전 2026-10-19      매수 4종목  /  매도 3종목</t>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,073억      오늘 2026-10-26  vs  5일전 2026-10-19      매수 4종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B104" s="4" t="n"/>
@@ -4164,88 +4164,88 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>프로티나</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B107" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C107" s="11" t="n">
-        <v>270345835</v>
+        <v>146216965</v>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>2.67%→2.22%</t>
+          <t>6.77%→5.09%</t>
         </is>
       </c>
       <c r="E107" s="13" t="inlineStr">
         <is>
-          <t>22→25</t>
+          <t>103→106</t>
         </is>
       </c>
       <c r="G107" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>와이바이오로직스</t>
         </is>
       </c>
       <c r="H107" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I107" s="15" t="n">
-        <v>-565787064</v>
+        <v>-84951020</v>
       </c>
       <c r="J107" s="16" t="inlineStr">
         <is>
-          <t>7.63%→5.02%</t>
+          <t>0.43%→0.23%</t>
         </is>
       </c>
       <c r="K107" s="13" t="inlineStr">
         <is>
-          <t>40→36</t>
+          <t>15→11</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>HLB이노베이션</t>
+          <t>프로티나</t>
         </is>
       </c>
       <c r="B108" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C108" s="11" t="n">
-        <v>99054216</v>
+        <v>270345835</v>
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>3.21%→2.44%</t>
+          <t>2.67%→2.22%</t>
         </is>
       </c>
       <c r="E108" s="13" t="inlineStr">
         <is>
-          <t>72→75</t>
+          <t>22→25</t>
         </is>
       </c>
       <c r="G108" s="14" t="inlineStr">
         <is>
-          <t>와이바이오로직스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H108" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I108" s="15" t="n">
-        <v>-84951020</v>
+        <v>-565787064</v>
       </c>
       <c r="J108" s="16" t="inlineStr">
         <is>
-          <t>0.43%→0.23%</t>
+          <t>7.63%→5.02%</t>
         </is>
       </c>
       <c r="K108" s="13" t="inlineStr">
         <is>
-          <t>15→11</t>
+          <t>40→36</t>
         </is>
       </c>
     </row>
@@ -4296,23 +4296,23 @@
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>HLB이노베이션</t>
         </is>
       </c>
       <c r="B110" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C110" s="11" t="n">
-        <v>146216965</v>
+        <v>99054216</v>
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>6.77%→5.09%</t>
+          <t>3.21%→2.44%</t>
         </is>
       </c>
       <c r="E110" s="13" t="inlineStr">
         <is>
-          <t>103→106</t>
+          <t>72→75</t>
         </is>
       </c>
       <c r="G110" s="17" t="n"/>
@@ -5169,7 +5169,7 @@
     <row r="135" ht="19" customHeight="1">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 300억   ·   현금 4억(1.4%)      오늘 2026-10-26  vs  5일전 2026-10-19      매수 11종목  /  매도 22종목</t>
+          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 300억      오늘 2026-10-26  vs  5일전 2026-10-19      매수 11종목  /  매도 22종목</t>
         </is>
       </c>
       <c r="B135" s="4" t="n"/>
@@ -5346,88 +5346,88 @@
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="B140" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C140" s="11" t="n">
-        <v>282200066</v>
+        <v>422450099</v>
       </c>
       <c r="D140" s="12" t="inlineStr">
         <is>
-          <t>3.37%→4.29%</t>
+          <t>0.65%→2.07%</t>
         </is>
       </c>
       <c r="E140" s="13" t="inlineStr">
         <is>
-          <t>70→90</t>
+          <t>9→29</t>
         </is>
       </c>
       <c r="G140" s="14" t="inlineStr">
         <is>
-          <t>덕산하이메탈</t>
+          <t>피엠티</t>
         </is>
       </c>
       <c r="H140" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I140" s="15" t="n">
-        <v>-238000056</v>
+        <v>-71293767</v>
       </c>
       <c r="J140" s="16" t="inlineStr">
         <is>
-          <t>1.46%→0.64%</t>
+          <t>0.26%→0.01%</t>
         </is>
       </c>
       <c r="K140" s="13" t="inlineStr">
         <is>
-          <t>90→40</t>
+          <t>53→3</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="B141" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C141" s="11" t="n">
-        <v>422450099</v>
+        <v>282200066</v>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>0.65%→2.07%</t>
+          <t>3.37%→4.29%</t>
         </is>
       </c>
       <c r="E141" s="13" t="inlineStr">
         <is>
-          <t>9→29</t>
+          <t>70→90</t>
         </is>
       </c>
       <c r="G141" s="14" t="inlineStr">
         <is>
-          <t>피엠티</t>
+          <t>덕산하이메탈</t>
         </is>
       </c>
       <c r="H141" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I141" s="15" t="n">
-        <v>-71293767</v>
+        <v>-238000056</v>
       </c>
       <c r="J141" s="16" t="inlineStr">
         <is>
-          <t>0.26%→0.01%</t>
+          <t>1.46%→0.64%</t>
         </is>
       </c>
       <c r="K141" s="13" t="inlineStr">
         <is>
-          <t>53→3</t>
+          <t>90→40</t>
         </is>
       </c>
     </row>
@@ -5610,23 +5610,23 @@
     <row r="146">
       <c r="A146" s="10" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="B146" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>307317572</v>
+        <v>120636278</v>
       </c>
       <c r="D146" s="12" t="inlineStr">
         <is>
-          <t>2.69%→3.71%</t>
+          <t>0.53%→0.93%</t>
         </is>
       </c>
       <c r="E146" s="13" t="inlineStr">
         <is>
-          <t>18→25</t>
+          <t>9→16</t>
         </is>
       </c>
       <c r="G146" s="14" t="inlineStr">
@@ -5654,23 +5654,23 @@
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="B147" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C147" s="11" t="n">
-        <v>120636278</v>
+        <v>307317572</v>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>0.53%→0.93%</t>
+          <t>2.69%→3.71%</t>
         </is>
       </c>
       <c r="E147" s="13" t="inlineStr">
         <is>
-          <t>9→16</t>
+          <t>18→25</t>
         </is>
       </c>
       <c r="G147" s="14" t="inlineStr">
@@ -5803,23 +5803,23 @@
       <c r="E151" s="17" t="n"/>
       <c r="G151" s="14" t="inlineStr">
         <is>
-          <t>네패스</t>
+          <t>HLB이노베이션</t>
         </is>
       </c>
       <c r="H151" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I151" s="15" t="n">
-        <v>-108927526</v>
+        <v>-74426018</v>
       </c>
       <c r="J151" s="16" t="inlineStr">
         <is>
-          <t>0.91%→0.54%</t>
+          <t>0.92%→0.66%</t>
         </is>
       </c>
       <c r="K151" s="13" t="inlineStr">
         <is>
-          <t>27→16</t>
+          <t>40→29</t>
         </is>
       </c>
     </row>
@@ -5831,23 +5831,23 @@
       <c r="E152" s="17" t="n"/>
       <c r="G152" s="14" t="inlineStr">
         <is>
-          <t>HLB이노베이션</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H152" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I152" s="15" t="n">
-        <v>-74426018</v>
+        <v>-549312629</v>
       </c>
       <c r="J152" s="16" t="inlineStr">
         <is>
-          <t>0.92%→0.66%</t>
+          <t>2.89%→1.01%</t>
         </is>
       </c>
       <c r="K152" s="13" t="inlineStr">
         <is>
-          <t>40→29</t>
+          <t>17→6</t>
         </is>
       </c>
     </row>
@@ -5859,23 +5859,23 @@
       <c r="E153" s="17" t="n"/>
       <c r="G153" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>네패스</t>
         </is>
       </c>
       <c r="H153" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I153" s="15" t="n">
-        <v>-549312629</v>
+        <v>-108927526</v>
       </c>
       <c r="J153" s="16" t="inlineStr">
         <is>
-          <t>2.89%→1.01%</t>
+          <t>0.91%→0.54%</t>
         </is>
       </c>
       <c r="K153" s="13" t="inlineStr">
         <is>
-          <t>17→6</t>
+          <t>27→16</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
     <row r="161" ht="19" customHeight="1">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 56억   ·   현금 1억(1.7%)      오늘 2026-10-26  vs  5일전 2026-10-19      매수 4종목  /  매도 3종목</t>
+          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 56억      오늘 2026-10-26  vs  5일전 2026-10-19      매수 4종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B161" s="4" t="n"/>

--- a/reports/pdf_rolling5_20261026.xlsx
+++ b/reports/pdf_rolling5_20261026.xlsx
@@ -1186,23 +1186,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>2838864800</v>
+        <v>560019758</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>1.45%→2.03%</t>
+          <t>0.43%→0.50%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>25→37</t>
+          <t>34→46</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1230,23 +1230,23 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>560019758</v>
+        <v>403166514</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>0.43%→0.50%</t>
+          <t>1.43%→1.44%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>34→46</t>
+          <t>173→185</t>
         </is>
       </c>
       <c r="G19" s="17" t="n"/>
@@ -1258,23 +1258,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>403166514</v>
+        <v>2838864800</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>1.43%→1.44%</t>
+          <t>1.45%→2.03%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>173→185</t>
+          <t>25→37</t>
         </is>
       </c>
       <c r="G20" s="17" t="n"/>
@@ -2228,23 +2228,23 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>코세스  (신규)</t>
         </is>
       </c>
       <c r="B50" s="11" t="n">
         <v>250</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>6690753650</v>
+        <v>6583503591</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>2.91%→6.27%</t>
+          <t>0.00%→3.08%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>250→500</t>
+          <t>0→250</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
@@ -2272,23 +2272,23 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>코세스  (신규)</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="B51" s="11" t="n">
         <v>250</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>6583503591</v>
+        <v>6690753650</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>0.00%→3.08%</t>
+          <t>2.91%→6.27%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>0→250</t>
+          <t>250→500</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
@@ -2469,23 +2469,23 @@
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
         <v>-105</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-7636864166</v>
+        <v>-5391542941</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>4.63%→0.85%</t>
+          <t>4.01%→1.80%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>130→25</t>
+          <t>180→75</t>
         </is>
       </c>
     </row>
@@ -2513,23 +2513,23 @@
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-105</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-5391542941</v>
+        <v>-7636864166</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>4.01%→1.80%</t>
+          <t>4.63%→0.85%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>180→75</t>
+          <t>130→25</t>
         </is>
       </c>
     </row>
@@ -3009,23 +3009,23 @@
       <c r="E68" s="17" t="n"/>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>에이비엘바이오  (편출)</t>
         </is>
       </c>
       <c r="H68" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-4240502313</v>
+        <v>-715275390</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>5.01%→2.78%</t>
+          <t>0.30%→0.00%</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
         <is>
-          <t>60→35</t>
+          <t>25→0</t>
         </is>
       </c>
     </row>
@@ -3065,23 +3065,23 @@
       <c r="E70" s="17" t="n"/>
       <c r="G70" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오  (편출)</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H70" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I70" s="15" t="n">
-        <v>-715275390</v>
+        <v>-4240502313</v>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
-          <t>0.30%→0.00%</t>
+          <t>5.01%→2.78%</t>
         </is>
       </c>
       <c r="K70" s="13" t="inlineStr">
         <is>
-          <t>25→0</t>
+          <t>60→35</t>
         </is>
       </c>
     </row>
@@ -3914,23 +3914,23 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>선익시스템</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B97" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C97" s="11" t="n">
-        <v>38079976</v>
+        <v>49369569</v>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>1.32%→1.46%</t>
+          <t>2.26%→2.45%</t>
         </is>
       </c>
       <c r="E97" s="13" t="inlineStr">
         <is>
-          <t>58→65</t>
+          <t>77→84</t>
         </is>
       </c>
       <c r="G97" s="14" t="inlineStr">
@@ -3958,23 +3958,23 @@
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>선익시스템</t>
         </is>
       </c>
       <c r="B98" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C98" s="11" t="n">
-        <v>49369569</v>
+        <v>38079976</v>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>2.26%→2.45%</t>
+          <t>1.32%→1.46%</t>
         </is>
       </c>
       <c r="E98" s="13" t="inlineStr">
         <is>
-          <t>77→84</t>
+          <t>58→65</t>
         </is>
       </c>
       <c r="G98" s="14" t="inlineStr">
@@ -4002,23 +4002,23 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>나노신소재</t>
         </is>
       </c>
       <c r="B99" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C99" s="11" t="n">
-        <v>36710377</v>
+        <v>21427187</v>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>1.84%→1.98%</t>
+          <t>0.12%→0.21%</t>
         </is>
       </c>
       <c r="E99" s="13" t="inlineStr">
         <is>
-          <t>72→78</t>
+          <t>8→14</t>
         </is>
       </c>
       <c r="G99" s="17" t="n"/>
@@ -4030,23 +4030,23 @@
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>나노신소재</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B100" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C100" s="11" t="n">
-        <v>21427187</v>
+        <v>36710377</v>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>0.12%→0.21%</t>
+          <t>1.84%→1.98%</t>
         </is>
       </c>
       <c r="E100" s="13" t="inlineStr">
         <is>
-          <t>8→14</t>
+          <t>72→78</t>
         </is>
       </c>
       <c r="G100" s="17" t="n"/>
@@ -4185,90 +4185,90 @@
       </c>
       <c r="G107" s="14" t="inlineStr">
         <is>
-          <t>와이바이오로직스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H107" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I107" s="15" t="n">
-        <v>-84951020</v>
+        <v>-565787064</v>
       </c>
       <c r="J107" s="16" t="inlineStr">
         <is>
-          <t>0.43%→0.23%</t>
+          <t>7.63%→5.02%</t>
         </is>
       </c>
       <c r="K107" s="13" t="inlineStr">
         <is>
-          <t>15→11</t>
+          <t>40→36</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>프로티나</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="B108" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C108" s="11" t="n">
-        <v>270345835</v>
+        <v>275323434</v>
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>2.67%→2.22%</t>
+          <t>6.81%→5.24%</t>
         </is>
       </c>
       <c r="E108" s="13" t="inlineStr">
         <is>
-          <t>22→25</t>
+          <t>55→58</t>
         </is>
       </c>
       <c r="G108" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>와이바이오로직스</t>
         </is>
       </c>
       <c r="H108" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I108" s="15" t="n">
-        <v>-565787064</v>
+        <v>-84951020</v>
       </c>
       <c r="J108" s="16" t="inlineStr">
         <is>
-          <t>7.63%→5.02%</t>
+          <t>0.43%→0.23%</t>
         </is>
       </c>
       <c r="K108" s="13" t="inlineStr">
         <is>
-          <t>40→36</t>
+          <t>15→11</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>HLB이노베이션</t>
         </is>
       </c>
       <c r="B109" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C109" s="11" t="n">
-        <v>275323434</v>
+        <v>99054216</v>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>6.81%→5.24%</t>
+          <t>3.21%→2.44%</t>
         </is>
       </c>
       <c r="E109" s="13" t="inlineStr">
         <is>
-          <t>55→58</t>
+          <t>72→75</t>
         </is>
       </c>
       <c r="G109" s="14" t="inlineStr">
@@ -4296,23 +4296,23 @@
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>HLB이노베이션</t>
+          <t>프로티나</t>
         </is>
       </c>
       <c r="B110" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C110" s="11" t="n">
-        <v>99054216</v>
+        <v>270345835</v>
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>3.21%→2.44%</t>
+          <t>2.67%→2.22%</t>
         </is>
       </c>
       <c r="E110" s="13" t="inlineStr">
         <is>
-          <t>72→75</t>
+          <t>22→25</t>
         </is>
       </c>
       <c r="G110" s="17" t="n"/>
@@ -5118,23 +5118,23 @@
       <c r="E132" s="17" t="n"/>
       <c r="G132" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="H132" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I132" s="15" t="n">
-        <v>-173731959</v>
+        <v>-273103935</v>
       </c>
       <c r="J132" s="16" t="inlineStr">
         <is>
-          <t>2.57%→2.14%</t>
+          <t>4.46%→3.93%</t>
         </is>
       </c>
       <c r="K132" s="13" t="inlineStr">
         <is>
-          <t>46→42</t>
+          <t>53→49</t>
         </is>
       </c>
     </row>
@@ -5146,23 +5146,23 @@
       <c r="E133" s="17" t="n"/>
       <c r="G133" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H133" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I133" s="15" t="n">
-        <v>-273103935</v>
+        <v>-173731959</v>
       </c>
       <c r="J133" s="16" t="inlineStr">
         <is>
-          <t>4.46%→3.93%</t>
+          <t>2.57%→2.14%</t>
         </is>
       </c>
       <c r="K133" s="13" t="inlineStr">
         <is>
-          <t>53→49</t>
+          <t>46→42</t>
         </is>
       </c>
     </row>
@@ -5367,23 +5367,23 @@
       </c>
       <c r="G140" s="14" t="inlineStr">
         <is>
-          <t>피엠티</t>
+          <t>덕산하이메탈</t>
         </is>
       </c>
       <c r="H140" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I140" s="15" t="n">
-        <v>-71293767</v>
+        <v>-238000056</v>
       </c>
       <c r="J140" s="16" t="inlineStr">
         <is>
-          <t>0.26%→0.01%</t>
+          <t>1.46%→0.64%</t>
         </is>
       </c>
       <c r="K140" s="13" t="inlineStr">
         <is>
-          <t>53→3</t>
+          <t>90→40</t>
         </is>
       </c>
     </row>
@@ -5411,23 +5411,23 @@
       </c>
       <c r="G141" s="14" t="inlineStr">
         <is>
-          <t>덕산하이메탈</t>
+          <t>피엠티</t>
         </is>
       </c>
       <c r="H141" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I141" s="15" t="n">
-        <v>-238000056</v>
+        <v>-71293767</v>
       </c>
       <c r="J141" s="16" t="inlineStr">
         <is>
-          <t>1.46%→0.64%</t>
+          <t>0.26%→0.01%</t>
         </is>
       </c>
       <c r="K141" s="13" t="inlineStr">
         <is>
-          <t>90→40</t>
+          <t>53→3</t>
         </is>
       </c>
     </row>
@@ -5522,23 +5522,23 @@
     <row r="144">
       <c r="A144" s="10" t="inlineStr">
         <is>
-          <t>선익시스템  (신규)</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B144" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>325125076</v>
+        <v>89887521</v>
       </c>
       <c r="D144" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.10%</t>
+          <t>0.72%→1.01%</t>
         </is>
       </c>
       <c r="E144" s="13" t="inlineStr">
         <is>
-          <t>0→9</t>
+          <t>21→30</t>
         </is>
       </c>
       <c r="G144" s="14" t="inlineStr">
@@ -5566,23 +5566,23 @@
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>선익시스템  (신규)</t>
         </is>
       </c>
       <c r="B145" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C145" s="11" t="n">
-        <v>89887521</v>
+        <v>325125076</v>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>0.72%→1.01%</t>
+          <t>0.00%→1.10%</t>
         </is>
       </c>
       <c r="E145" s="13" t="inlineStr">
         <is>
-          <t>21→30</t>
+          <t>0→9</t>
         </is>
       </c>
       <c r="G145" s="14" t="inlineStr">
@@ -5610,23 +5610,23 @@
     <row r="146">
       <c r="A146" s="10" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="B146" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>120636278</v>
+        <v>307317572</v>
       </c>
       <c r="D146" s="12" t="inlineStr">
         <is>
-          <t>0.53%→0.93%</t>
+          <t>2.69%→3.71%</t>
         </is>
       </c>
       <c r="E146" s="13" t="inlineStr">
         <is>
-          <t>9→16</t>
+          <t>18→25</t>
         </is>
       </c>
       <c r="G146" s="14" t="inlineStr">
@@ -5654,23 +5654,23 @@
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="B147" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C147" s="11" t="n">
-        <v>307317572</v>
+        <v>120636278</v>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>2.69%→3.71%</t>
+          <t>0.53%→0.93%</t>
         </is>
       </c>
       <c r="E147" s="13" t="inlineStr">
         <is>
-          <t>18→25</t>
+          <t>9→16</t>
         </is>
       </c>
       <c r="G147" s="14" t="inlineStr">
@@ -5971,23 +5971,23 @@
       <c r="E157" s="17" t="n"/>
       <c r="G157" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="H157" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I157" s="15" t="n">
-        <v>-172210041</v>
+        <v>-118490028</v>
       </c>
       <c r="J157" s="16" t="inlineStr">
         <is>
-          <t>1.03%→0.44%</t>
+          <t>3.64%→3.20%</t>
         </is>
       </c>
       <c r="K157" s="13" t="inlineStr">
         <is>
-          <t>7→3</t>
+          <t>36→32</t>
         </is>
       </c>
     </row>
@@ -5999,23 +5999,23 @@
       <c r="E158" s="17" t="n"/>
       <c r="G158" s="14" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H158" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I158" s="15" t="n">
-        <v>-118490028</v>
+        <v>-172210041</v>
       </c>
       <c r="J158" s="16" t="inlineStr">
         <is>
-          <t>3.64%→3.20%</t>
+          <t>1.03%→0.44%</t>
         </is>
       </c>
       <c r="K158" s="13" t="inlineStr">
         <is>
-          <t>36→32</t>
+          <t>7→3</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20261026.xlsx
+++ b/reports/pdf_rolling5_20261026.xlsx
@@ -1186,23 +1186,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>560019758</v>
+        <v>2838864800</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>0.43%→0.50%</t>
+          <t>1.45%→2.03%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>34→46</t>
+          <t>25→37</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1258,23 +1258,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>2838864800</v>
+        <v>560019758</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>1.45%→2.03%</t>
+          <t>0.43%→0.50%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>25→37</t>
+          <t>34→46</t>
         </is>
       </c>
       <c r="G20" s="17" t="n"/>
@@ -2469,23 +2469,23 @@
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
         <v>-105</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-5391542941</v>
+        <v>-7636864166</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>4.01%→1.80%</t>
+          <t>4.63%→0.85%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>180→75</t>
+          <t>130→25</t>
         </is>
       </c>
     </row>
@@ -2513,23 +2513,23 @@
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-105</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-7636864166</v>
+        <v>-5391542941</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>4.63%→0.85%</t>
+          <t>4.01%→1.80%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>130→25</t>
+          <t>180→75</t>
         </is>
       </c>
     </row>
@@ -2689,23 +2689,23 @@
       </c>
       <c r="G60" s="14" t="inlineStr">
         <is>
-          <t>비츠로셀  (편출)</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H60" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-795300434</v>
+        <v>-5936703238</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>0.34%→0.00%</t>
+          <t>6.50%→3.34%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>110→60</t>
         </is>
       </c>
     </row>
@@ -2733,23 +2733,23 @@
       </c>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>비츠로셀  (편출)</t>
         </is>
       </c>
       <c r="H61" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-5936703238</v>
+        <v>-795300434</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>6.50%→3.34%</t>
+          <t>0.34%→0.00%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
         <is>
-          <t>110→60</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
@@ -2844,23 +2844,23 @@
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B64" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>1002870547</v>
+        <v>1715670936</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>0.47%→0.91%</t>
+          <t>5.87%→6.43%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>14→29</t>
+          <t>105→120</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
@@ -2888,23 +2888,23 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B65" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>1715670936</v>
+        <v>1002870547</v>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>5.87%→6.43%</t>
+          <t>0.47%→0.91%</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
-          <t>105→120</t>
+          <t>14→29</t>
         </is>
       </c>
       <c r="G65" s="14" t="inlineStr">
@@ -3009,23 +3009,23 @@
       <c r="E68" s="17" t="n"/>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오  (편출)</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H68" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-715275390</v>
+        <v>-4240502313</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>0.30%→0.00%</t>
+          <t>5.01%→2.78%</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
         <is>
-          <t>25→0</t>
+          <t>60→35</t>
         </is>
       </c>
     </row>
@@ -3037,23 +3037,23 @@
       <c r="E69" s="17" t="n"/>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>에이비엘바이오  (편출)</t>
         </is>
       </c>
       <c r="H69" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-1584000864</v>
+        <v>-715275390</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>1.45%→0.74%</t>
+          <t>0.30%→0.00%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
         <is>
-          <t>50→25</t>
+          <t>25→0</t>
         </is>
       </c>
     </row>
@@ -3065,23 +3065,23 @@
       <c r="E70" s="17" t="n"/>
       <c r="G70" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H70" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I70" s="15" t="n">
-        <v>-4240502313</v>
+        <v>-1584000864</v>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
-          <t>5.01%→2.78%</t>
+          <t>1.45%→0.74%</t>
         </is>
       </c>
       <c r="K70" s="13" t="inlineStr">
         <is>
-          <t>60→35</t>
+          <t>50→25</t>
         </is>
       </c>
     </row>
@@ -3093,23 +3093,23 @@
       <c r="E71" s="17" t="n"/>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H71" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>-3564001944</v>
+        <v>-1080288589</v>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>3.16%→1.74%</t>
+          <t>1.15%→0.76%</t>
         </is>
       </c>
       <c r="K71" s="13" t="inlineStr">
         <is>
-          <t>49→25</t>
+          <t>60→36</t>
         </is>
       </c>
     </row>
@@ -3121,23 +3121,23 @@
       <c r="E72" s="17" t="n"/>
       <c r="G72" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H72" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I72" s="15" t="n">
-        <v>-1080288589</v>
+        <v>-3564001944</v>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
-          <t>1.15%→0.76%</t>
+          <t>3.16%→1.74%</t>
         </is>
       </c>
       <c r="K72" s="13" t="inlineStr">
         <is>
-          <t>60→36</t>
+          <t>49→25</t>
         </is>
       </c>
     </row>
@@ -3205,23 +3205,23 @@
       <c r="E75" s="17" t="n"/>
       <c r="G75" s="14" t="inlineStr">
         <is>
-          <t>보로노이  (편출)</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H75" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I75" s="15" t="n">
-        <v>-650496355</v>
+        <v>-1861201015</v>
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
-          <t>0.28%→0.00%</t>
+          <t>2.67%→2.07%</t>
         </is>
       </c>
       <c r="K75" s="13" t="inlineStr">
         <is>
-          <t>8→0</t>
+          <t>27→19</t>
         </is>
       </c>
     </row>
@@ -3233,23 +3233,23 @@
       <c r="E76" s="17" t="n"/>
       <c r="G76" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>보로노이  (편출)</t>
         </is>
       </c>
       <c r="H76" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I76" s="15" t="n">
-        <v>-1861201015</v>
+        <v>-650496355</v>
       </c>
       <c r="J76" s="16" t="inlineStr">
         <is>
-          <t>2.67%→2.07%</t>
+          <t>0.28%→0.00%</t>
         </is>
       </c>
       <c r="K76" s="13" t="inlineStr">
         <is>
-          <t>27→19</t>
+          <t>8→0</t>
         </is>
       </c>
     </row>
@@ -4164,23 +4164,23 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>프로티나</t>
         </is>
       </c>
       <c r="B107" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C107" s="11" t="n">
-        <v>146216965</v>
+        <v>270345835</v>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>6.77%→5.09%</t>
+          <t>2.67%→2.22%</t>
         </is>
       </c>
       <c r="E107" s="13" t="inlineStr">
         <is>
-          <t>103→106</t>
+          <t>22→25</t>
         </is>
       </c>
       <c r="G107" s="14" t="inlineStr">
@@ -4208,23 +4208,23 @@
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>HLB이노베이션</t>
         </is>
       </c>
       <c r="B108" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C108" s="11" t="n">
-        <v>275323434</v>
+        <v>99054216</v>
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>6.81%→5.24%</t>
+          <t>3.21%→2.44%</t>
         </is>
       </c>
       <c r="E108" s="13" t="inlineStr">
         <is>
-          <t>55→58</t>
+          <t>72→75</t>
         </is>
       </c>
       <c r="G108" s="14" t="inlineStr">
@@ -4252,23 +4252,23 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>HLB이노베이션</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B109" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C109" s="11" t="n">
-        <v>99054216</v>
+        <v>146216965</v>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>3.21%→2.44%</t>
+          <t>6.77%→5.09%</t>
         </is>
       </c>
       <c r="E109" s="13" t="inlineStr">
         <is>
-          <t>72→75</t>
+          <t>103→106</t>
         </is>
       </c>
       <c r="G109" s="14" t="inlineStr">
@@ -4296,23 +4296,23 @@
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>프로티나</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="B110" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C110" s="11" t="n">
-        <v>270345835</v>
+        <v>275323434</v>
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>2.67%→2.22%</t>
+          <t>6.81%→5.24%</t>
         </is>
       </c>
       <c r="E110" s="13" t="inlineStr">
         <is>
-          <t>22→25</t>
+          <t>55→58</t>
         </is>
       </c>
       <c r="G110" s="17" t="n"/>
@@ -5118,23 +5118,23 @@
       <c r="E132" s="17" t="n"/>
       <c r="G132" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H132" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I132" s="15" t="n">
-        <v>-273103935</v>
+        <v>-173731959</v>
       </c>
       <c r="J132" s="16" t="inlineStr">
         <is>
-          <t>4.46%→3.93%</t>
+          <t>2.57%→2.14%</t>
         </is>
       </c>
       <c r="K132" s="13" t="inlineStr">
         <is>
-          <t>53→49</t>
+          <t>46→42</t>
         </is>
       </c>
     </row>
@@ -5146,23 +5146,23 @@
       <c r="E133" s="17" t="n"/>
       <c r="G133" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="H133" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I133" s="15" t="n">
-        <v>-173731959</v>
+        <v>-273103935</v>
       </c>
       <c r="J133" s="16" t="inlineStr">
         <is>
-          <t>2.57%→2.14%</t>
+          <t>4.46%→3.93%</t>
         </is>
       </c>
       <c r="K133" s="13" t="inlineStr">
         <is>
-          <t>46→42</t>
+          <t>53→49</t>
         </is>
       </c>
     </row>
@@ -5367,23 +5367,23 @@
       </c>
       <c r="G140" s="14" t="inlineStr">
         <is>
-          <t>덕산하이메탈</t>
+          <t>피엠티</t>
         </is>
       </c>
       <c r="H140" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I140" s="15" t="n">
-        <v>-238000056</v>
+        <v>-71293767</v>
       </c>
       <c r="J140" s="16" t="inlineStr">
         <is>
-          <t>1.46%→0.64%</t>
+          <t>0.26%→0.01%</t>
         </is>
       </c>
       <c r="K140" s="13" t="inlineStr">
         <is>
-          <t>90→40</t>
+          <t>53→3</t>
         </is>
       </c>
     </row>
@@ -5411,23 +5411,23 @@
       </c>
       <c r="G141" s="14" t="inlineStr">
         <is>
-          <t>피엠티</t>
+          <t>덕산하이메탈</t>
         </is>
       </c>
       <c r="H141" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I141" s="15" t="n">
-        <v>-71293767</v>
+        <v>-238000056</v>
       </c>
       <c r="J141" s="16" t="inlineStr">
         <is>
-          <t>0.26%→0.01%</t>
+          <t>1.46%→0.64%</t>
         </is>
       </c>
       <c r="K141" s="13" t="inlineStr">
         <is>
-          <t>53→3</t>
+          <t>90→40</t>
         </is>
       </c>
     </row>
@@ -5522,23 +5522,23 @@
     <row r="144">
       <c r="A144" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>선익시스템  (신규)</t>
         </is>
       </c>
       <c r="B144" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>89887521</v>
+        <v>325125076</v>
       </c>
       <c r="D144" s="12" t="inlineStr">
         <is>
-          <t>0.72%→1.01%</t>
+          <t>0.00%→1.10%</t>
         </is>
       </c>
       <c r="E144" s="13" t="inlineStr">
         <is>
-          <t>21→30</t>
+          <t>0→9</t>
         </is>
       </c>
       <c r="G144" s="14" t="inlineStr">
@@ -5566,23 +5566,23 @@
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>선익시스템  (신규)</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B145" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C145" s="11" t="n">
-        <v>325125076</v>
+        <v>89887521</v>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.10%</t>
+          <t>0.72%→1.01%</t>
         </is>
       </c>
       <c r="E145" s="13" t="inlineStr">
         <is>
-          <t>0→9</t>
+          <t>21→30</t>
         </is>
       </c>
       <c r="G145" s="14" t="inlineStr">
@@ -5610,23 +5610,23 @@
     <row r="146">
       <c r="A146" s="10" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="B146" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>307317572</v>
+        <v>120636278</v>
       </c>
       <c r="D146" s="12" t="inlineStr">
         <is>
-          <t>2.69%→3.71%</t>
+          <t>0.53%→0.93%</t>
         </is>
       </c>
       <c r="E146" s="13" t="inlineStr">
         <is>
-          <t>18→25</t>
+          <t>9→16</t>
         </is>
       </c>
       <c r="G146" s="14" t="inlineStr">
@@ -5654,23 +5654,23 @@
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="B147" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C147" s="11" t="n">
-        <v>120636278</v>
+        <v>307317572</v>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>0.53%→0.93%</t>
+          <t>2.69%→3.71%</t>
         </is>
       </c>
       <c r="E147" s="13" t="inlineStr">
         <is>
-          <t>9→16</t>
+          <t>18→25</t>
         </is>
       </c>
       <c r="G147" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20261026.xlsx
+++ b/reports/pdf_rolling5_20261026.xlsx
@@ -1186,23 +1186,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>2838864800</v>
+        <v>560019758</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>1.45%→2.03%</t>
+          <t>0.43%→0.50%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>25→37</t>
+          <t>34→46</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1230,23 +1230,23 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>403166514</v>
+        <v>2838864800</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>1.43%→1.44%</t>
+          <t>1.45%→2.03%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>173→185</t>
+          <t>25→37</t>
         </is>
       </c>
       <c r="G19" s="17" t="n"/>
@@ -1258,23 +1258,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>560019758</v>
+        <v>403166514</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>0.43%→0.50%</t>
+          <t>1.43%→1.44%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>34→46</t>
+          <t>173→185</t>
         </is>
       </c>
       <c r="G20" s="17" t="n"/>
@@ -1844,23 +1844,23 @@
       <c r="E37" s="17" t="n"/>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H37" s="15" t="n">
         <v>-22</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-1062078640</v>
+        <v>-2829453105</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>7.43%→6.97%</t>
+          <t>3.97%→2.49%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
         <is>
-          <t>462→440</t>
+          <t>81→59</t>
         </is>
       </c>
     </row>
@@ -1872,23 +1872,23 @@
       <c r="E38" s="17" t="n"/>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="H38" s="15" t="n">
         <v>-22</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-2829453105</v>
+        <v>-1062078640</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>3.97%→2.49%</t>
+          <t>7.43%→6.97%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>81→59</t>
+          <t>462→440</t>
         </is>
       </c>
     </row>
@@ -2469,23 +2469,23 @@
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
         <v>-105</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-7636864166</v>
+        <v>-5391542941</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>4.63%→0.85%</t>
+          <t>4.01%→1.80%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>130→25</t>
+          <t>180→75</t>
         </is>
       </c>
     </row>
@@ -2513,23 +2513,23 @@
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-105</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-5391542941</v>
+        <v>-7636864166</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>4.01%→1.80%</t>
+          <t>4.63%→0.85%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>180→75</t>
+          <t>130→25</t>
         </is>
       </c>
     </row>
@@ -2777,23 +2777,23 @@
       </c>
       <c r="G62" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="H62" s="15" t="n">
         <v>-49</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-3279277789</v>
+        <v>-2121505157</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>2.86%→1.25%</t>
+          <t>1.91%→1.01%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
         <is>
-          <t>89→40</t>
+          <t>99→50</t>
         </is>
       </c>
     </row>
@@ -2821,46 +2821,46 @@
       </c>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H63" s="15" t="n">
         <v>-49</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-2121505157</v>
+        <v>-3279277789</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>1.91%→1.01%</t>
+          <t>2.86%→1.25%</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
         <is>
-          <t>99→50</t>
+          <t>89→40</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B64" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>1715670936</v>
+        <v>1002870547</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>5.87%→6.43%</t>
+          <t>0.47%→0.91%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>105→120</t>
+          <t>14→29</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
@@ -2888,23 +2888,23 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B65" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>1002870547</v>
+        <v>1715670936</v>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>0.47%→0.91%</t>
+          <t>5.87%→6.43%</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
-          <t>14→29</t>
+          <t>105→120</t>
         </is>
       </c>
       <c r="G65" s="14" t="inlineStr">
@@ -3009,23 +3009,23 @@
       <c r="E68" s="17" t="n"/>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>에이비엘바이오  (편출)</t>
         </is>
       </c>
       <c r="H68" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-4240502313</v>
+        <v>-715275390</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>5.01%→2.78%</t>
+          <t>0.30%→0.00%</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
         <is>
-          <t>60→35</t>
+          <t>25→0</t>
         </is>
       </c>
     </row>
@@ -3037,23 +3037,23 @@
       <c r="E69" s="17" t="n"/>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오  (편출)</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H69" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-715275390</v>
+        <v>-1584000864</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>0.30%→0.00%</t>
+          <t>1.45%→0.74%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
         <is>
-          <t>25→0</t>
+          <t>50→25</t>
         </is>
       </c>
     </row>
@@ -3065,23 +3065,23 @@
       <c r="E70" s="17" t="n"/>
       <c r="G70" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H70" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I70" s="15" t="n">
-        <v>-1584000864</v>
+        <v>-4240502313</v>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
-          <t>1.45%→0.74%</t>
+          <t>5.01%→2.78%</t>
         </is>
       </c>
       <c r="K70" s="13" t="inlineStr">
         <is>
-          <t>50→25</t>
+          <t>60→35</t>
         </is>
       </c>
     </row>
@@ -3914,23 +3914,23 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>선익시스템</t>
         </is>
       </c>
       <c r="B97" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C97" s="11" t="n">
-        <v>49369569</v>
+        <v>38079976</v>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>2.26%→2.45%</t>
+          <t>1.32%→1.46%</t>
         </is>
       </c>
       <c r="E97" s="13" t="inlineStr">
         <is>
-          <t>77→84</t>
+          <t>58→65</t>
         </is>
       </c>
       <c r="G97" s="14" t="inlineStr">
@@ -3958,23 +3958,23 @@
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>선익시스템</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B98" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C98" s="11" t="n">
-        <v>38079976</v>
+        <v>49369569</v>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>1.32%→1.46%</t>
+          <t>2.26%→2.45%</t>
         </is>
       </c>
       <c r="E98" s="13" t="inlineStr">
         <is>
-          <t>58→65</t>
+          <t>77→84</t>
         </is>
       </c>
       <c r="G98" s="14" t="inlineStr">
@@ -4164,111 +4164,111 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>프로티나</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="B107" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C107" s="11" t="n">
-        <v>270345835</v>
+        <v>275323434</v>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>2.67%→2.22%</t>
+          <t>6.81%→5.24%</t>
         </is>
       </c>
       <c r="E107" s="13" t="inlineStr">
         <is>
-          <t>22→25</t>
+          <t>55→58</t>
         </is>
       </c>
       <c r="G107" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>와이바이오로직스</t>
         </is>
       </c>
       <c r="H107" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I107" s="15" t="n">
-        <v>-565787064</v>
+        <v>-84951020</v>
       </c>
       <c r="J107" s="16" t="inlineStr">
         <is>
-          <t>7.63%→5.02%</t>
+          <t>0.43%→0.23%</t>
         </is>
       </c>
       <c r="K107" s="13" t="inlineStr">
         <is>
-          <t>40→36</t>
+          <t>15→11</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>HLB이노베이션</t>
+          <t>프로티나</t>
         </is>
       </c>
       <c r="B108" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C108" s="11" t="n">
-        <v>99054216</v>
+        <v>270345835</v>
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>3.21%→2.44%</t>
+          <t>2.67%→2.22%</t>
         </is>
       </c>
       <c r="E108" s="13" t="inlineStr">
         <is>
-          <t>72→75</t>
+          <t>22→25</t>
         </is>
       </c>
       <c r="G108" s="14" t="inlineStr">
         <is>
-          <t>와이바이오로직스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H108" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I108" s="15" t="n">
-        <v>-84951020</v>
+        <v>-565787064</v>
       </c>
       <c r="J108" s="16" t="inlineStr">
         <is>
-          <t>0.43%→0.23%</t>
+          <t>7.63%→5.02%</t>
         </is>
       </c>
       <c r="K108" s="13" t="inlineStr">
         <is>
-          <t>15→11</t>
+          <t>40→36</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>HLB이노베이션</t>
         </is>
       </c>
       <c r="B109" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C109" s="11" t="n">
-        <v>146216965</v>
+        <v>99054216</v>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>6.77%→5.09%</t>
+          <t>3.21%→2.44%</t>
         </is>
       </c>
       <c r="E109" s="13" t="inlineStr">
         <is>
-          <t>103→106</t>
+          <t>72→75</t>
         </is>
       </c>
       <c r="G109" s="14" t="inlineStr">
@@ -4296,23 +4296,23 @@
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B110" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C110" s="11" t="n">
-        <v>275323434</v>
+        <v>146216965</v>
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>6.81%→5.24%</t>
+          <t>6.77%→5.09%</t>
         </is>
       </c>
       <c r="E110" s="13" t="inlineStr">
         <is>
-          <t>55→58</t>
+          <t>103→106</t>
         </is>
       </c>
       <c r="G110" s="17" t="n"/>
@@ -5118,23 +5118,23 @@
       <c r="E132" s="17" t="n"/>
       <c r="G132" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="H132" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I132" s="15" t="n">
-        <v>-173731959</v>
+        <v>-273103935</v>
       </c>
       <c r="J132" s="16" t="inlineStr">
         <is>
-          <t>2.57%→2.14%</t>
+          <t>4.46%→3.93%</t>
         </is>
       </c>
       <c r="K132" s="13" t="inlineStr">
         <is>
-          <t>46→42</t>
+          <t>53→49</t>
         </is>
       </c>
     </row>
@@ -5146,23 +5146,23 @@
       <c r="E133" s="17" t="n"/>
       <c r="G133" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H133" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I133" s="15" t="n">
-        <v>-273103935</v>
+        <v>-173731959</v>
       </c>
       <c r="J133" s="16" t="inlineStr">
         <is>
-          <t>4.46%→3.93%</t>
+          <t>2.57%→2.14%</t>
         </is>
       </c>
       <c r="K133" s="13" t="inlineStr">
         <is>
-          <t>53→49</t>
+          <t>46→42</t>
         </is>
       </c>
     </row>
@@ -5367,23 +5367,23 @@
       </c>
       <c r="G140" s="14" t="inlineStr">
         <is>
-          <t>피엠티</t>
+          <t>덕산하이메탈</t>
         </is>
       </c>
       <c r="H140" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I140" s="15" t="n">
-        <v>-71293767</v>
+        <v>-238000056</v>
       </c>
       <c r="J140" s="16" t="inlineStr">
         <is>
-          <t>0.26%→0.01%</t>
+          <t>1.46%→0.64%</t>
         </is>
       </c>
       <c r="K140" s="13" t="inlineStr">
         <is>
-          <t>53→3</t>
+          <t>90→40</t>
         </is>
       </c>
     </row>
@@ -5411,23 +5411,23 @@
       </c>
       <c r="G141" s="14" t="inlineStr">
         <is>
-          <t>덕산하이메탈</t>
+          <t>피엠티</t>
         </is>
       </c>
       <c r="H141" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I141" s="15" t="n">
-        <v>-238000056</v>
+        <v>-71293767</v>
       </c>
       <c r="J141" s="16" t="inlineStr">
         <is>
-          <t>1.46%→0.64%</t>
+          <t>0.26%→0.01%</t>
         </is>
       </c>
       <c r="K141" s="13" t="inlineStr">
         <is>
-          <t>90→40</t>
+          <t>53→3</t>
         </is>
       </c>
     </row>
@@ -5522,23 +5522,23 @@
     <row r="144">
       <c r="A144" s="10" t="inlineStr">
         <is>
-          <t>선익시스템  (신규)</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B144" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>325125076</v>
+        <v>89887521</v>
       </c>
       <c r="D144" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.10%</t>
+          <t>0.72%→1.01%</t>
         </is>
       </c>
       <c r="E144" s="13" t="inlineStr">
         <is>
-          <t>0→9</t>
+          <t>21→30</t>
         </is>
       </c>
       <c r="G144" s="14" t="inlineStr">
@@ -5566,23 +5566,23 @@
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>선익시스템  (신규)</t>
         </is>
       </c>
       <c r="B145" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C145" s="11" t="n">
-        <v>89887521</v>
+        <v>325125076</v>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>0.72%→1.01%</t>
+          <t>0.00%→1.10%</t>
         </is>
       </c>
       <c r="E145" s="13" t="inlineStr">
         <is>
-          <t>21→30</t>
+          <t>0→9</t>
         </is>
       </c>
       <c r="G145" s="14" t="inlineStr">
@@ -5610,23 +5610,23 @@
     <row r="146">
       <c r="A146" s="10" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="B146" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>120636278</v>
+        <v>307317572</v>
       </c>
       <c r="D146" s="12" t="inlineStr">
         <is>
-          <t>0.53%→0.93%</t>
+          <t>2.69%→3.71%</t>
         </is>
       </c>
       <c r="E146" s="13" t="inlineStr">
         <is>
-          <t>9→16</t>
+          <t>18→25</t>
         </is>
       </c>
       <c r="G146" s="14" t="inlineStr">
@@ -5654,23 +5654,23 @@
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="B147" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C147" s="11" t="n">
-        <v>307317572</v>
+        <v>120636278</v>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>2.69%→3.71%</t>
+          <t>0.53%→0.93%</t>
         </is>
       </c>
       <c r="E147" s="13" t="inlineStr">
         <is>
-          <t>18→25</t>
+          <t>9→16</t>
         </is>
       </c>
       <c r="G147" s="14" t="inlineStr">
@@ -5803,23 +5803,23 @@
       <c r="E151" s="17" t="n"/>
       <c r="G151" s="14" t="inlineStr">
         <is>
-          <t>HLB이노베이션</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H151" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I151" s="15" t="n">
-        <v>-74426018</v>
+        <v>-549312629</v>
       </c>
       <c r="J151" s="16" t="inlineStr">
         <is>
-          <t>0.92%→0.66%</t>
+          <t>2.89%→1.01%</t>
         </is>
       </c>
       <c r="K151" s="13" t="inlineStr">
         <is>
-          <t>40→29</t>
+          <t>17→6</t>
         </is>
       </c>
     </row>
@@ -5831,23 +5831,23 @@
       <c r="E152" s="17" t="n"/>
       <c r="G152" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>네패스</t>
         </is>
       </c>
       <c r="H152" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I152" s="15" t="n">
-        <v>-549312629</v>
+        <v>-108927526</v>
       </c>
       <c r="J152" s="16" t="inlineStr">
         <is>
-          <t>2.89%→1.01%</t>
+          <t>0.91%→0.54%</t>
         </is>
       </c>
       <c r="K152" s="13" t="inlineStr">
         <is>
-          <t>17→6</t>
+          <t>27→16</t>
         </is>
       </c>
     </row>
@@ -5859,23 +5859,23 @@
       <c r="E153" s="17" t="n"/>
       <c r="G153" s="14" t="inlineStr">
         <is>
-          <t>네패스</t>
+          <t>HLB이노베이션</t>
         </is>
       </c>
       <c r="H153" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I153" s="15" t="n">
-        <v>-108927526</v>
+        <v>-74426018</v>
       </c>
       <c r="J153" s="16" t="inlineStr">
         <is>
-          <t>0.91%→0.54%</t>
+          <t>0.92%→0.66%</t>
         </is>
       </c>
       <c r="K153" s="13" t="inlineStr">
         <is>
-          <t>27→16</t>
+          <t>40→29</t>
         </is>
       </c>
     </row>
@@ -5971,23 +5971,23 @@
       <c r="E157" s="17" t="n"/>
       <c r="G157" s="14" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H157" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I157" s="15" t="n">
-        <v>-118490028</v>
+        <v>-172210041</v>
       </c>
       <c r="J157" s="16" t="inlineStr">
         <is>
-          <t>3.64%→3.20%</t>
+          <t>1.03%→0.44%</t>
         </is>
       </c>
       <c r="K157" s="13" t="inlineStr">
         <is>
-          <t>36→32</t>
+          <t>7→3</t>
         </is>
       </c>
     </row>
@@ -5999,23 +5999,23 @@
       <c r="E158" s="17" t="n"/>
       <c r="G158" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="H158" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I158" s="15" t="n">
-        <v>-172210041</v>
+        <v>-118490028</v>
       </c>
       <c r="J158" s="16" t="inlineStr">
         <is>
-          <t>1.03%→0.44%</t>
+          <t>3.64%→3.20%</t>
         </is>
       </c>
       <c r="K158" s="13" t="inlineStr">
         <is>
-          <t>7→3</t>
+          <t>36→32</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20261026.xlsx
+++ b/reports/pdf_rolling5_20261026.xlsx
@@ -1186,23 +1186,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>560019758</v>
+        <v>403166514</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>0.43%→0.50%</t>
+          <t>1.43%→1.44%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>34→46</t>
+          <t>173→185</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1258,23 +1258,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>403166514</v>
+        <v>560019758</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>1.43%→1.44%</t>
+          <t>0.43%→0.50%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>173→185</t>
+          <t>34→46</t>
         </is>
       </c>
       <c r="G20" s="17" t="n"/>
@@ -1844,23 +1844,23 @@
       <c r="E37" s="17" t="n"/>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="H37" s="15" t="n">
         <v>-22</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-2829453105</v>
+        <v>-1062078640</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>3.97%→2.49%</t>
+          <t>7.43%→6.97%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
         <is>
-          <t>81→59</t>
+          <t>462→440</t>
         </is>
       </c>
     </row>
@@ -1872,23 +1872,23 @@
       <c r="E38" s="17" t="n"/>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H38" s="15" t="n">
         <v>-22</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-1062078640</v>
+        <v>-2829453105</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>7.43%→6.97%</t>
+          <t>3.97%→2.49%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>462→440</t>
+          <t>81→59</t>
         </is>
       </c>
     </row>
@@ -2689,23 +2689,23 @@
       </c>
       <c r="G60" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>비츠로셀  (편출)</t>
         </is>
       </c>
       <c r="H60" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-5936703238</v>
+        <v>-795300434</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>6.50%→3.34%</t>
+          <t>0.34%→0.00%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
         <is>
-          <t>110→60</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
@@ -2733,23 +2733,23 @@
       </c>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>비츠로셀  (편출)</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H61" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-795300434</v>
+        <v>-5936703238</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>0.34%→0.00%</t>
+          <t>6.50%→3.34%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>110→60</t>
         </is>
       </c>
     </row>
@@ -2777,23 +2777,23 @@
       </c>
       <c r="G62" s="14" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H62" s="15" t="n">
         <v>-49</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-2121505157</v>
+        <v>-3279277789</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>1.91%→1.01%</t>
+          <t>2.86%→1.25%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
         <is>
-          <t>99→50</t>
+          <t>89→40</t>
         </is>
       </c>
     </row>
@@ -2821,23 +2821,23 @@
       </c>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="H63" s="15" t="n">
         <v>-49</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-3279277789</v>
+        <v>-2121505157</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>2.86%→1.25%</t>
+          <t>1.91%→1.01%</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
         <is>
-          <t>89→40</t>
+          <t>99→50</t>
         </is>
       </c>
     </row>
@@ -3009,23 +3009,23 @@
       <c r="E68" s="17" t="n"/>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오  (편출)</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H68" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-715275390</v>
+        <v>-1584000864</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>0.30%→0.00%</t>
+          <t>1.45%→0.74%</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
         <is>
-          <t>25→0</t>
+          <t>50→25</t>
         </is>
       </c>
     </row>
@@ -3037,23 +3037,23 @@
       <c r="E69" s="17" t="n"/>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>에이비엘바이오  (편출)</t>
         </is>
       </c>
       <c r="H69" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-1584000864</v>
+        <v>-715275390</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>1.45%→0.74%</t>
+          <t>0.30%→0.00%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
         <is>
-          <t>50→25</t>
+          <t>25→0</t>
         </is>
       </c>
     </row>
@@ -3093,23 +3093,23 @@
       <c r="E71" s="17" t="n"/>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H71" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>-1080288589</v>
+        <v>-3564001944</v>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>1.15%→0.76%</t>
+          <t>3.16%→1.74%</t>
         </is>
       </c>
       <c r="K71" s="13" t="inlineStr">
         <is>
-          <t>60→36</t>
+          <t>49→25</t>
         </is>
       </c>
     </row>
@@ -3121,23 +3121,23 @@
       <c r="E72" s="17" t="n"/>
       <c r="G72" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H72" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I72" s="15" t="n">
-        <v>-3564001944</v>
+        <v>-1080288589</v>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
-          <t>3.16%→1.74%</t>
+          <t>1.15%→0.76%</t>
         </is>
       </c>
       <c r="K72" s="13" t="inlineStr">
         <is>
-          <t>49→25</t>
+          <t>60→36</t>
         </is>
       </c>
     </row>
@@ -4164,111 +4164,111 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>HLB이노베이션</t>
         </is>
       </c>
       <c r="B107" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C107" s="11" t="n">
-        <v>275323434</v>
+        <v>99054216</v>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>6.81%→5.24%</t>
+          <t>3.21%→2.44%</t>
         </is>
       </c>
       <c r="E107" s="13" t="inlineStr">
         <is>
-          <t>55→58</t>
+          <t>72→75</t>
         </is>
       </c>
       <c r="G107" s="14" t="inlineStr">
         <is>
-          <t>와이바이오로직스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H107" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I107" s="15" t="n">
-        <v>-84951020</v>
+        <v>-565787064</v>
       </c>
       <c r="J107" s="16" t="inlineStr">
         <is>
-          <t>0.43%→0.23%</t>
+          <t>7.63%→5.02%</t>
         </is>
       </c>
       <c r="K107" s="13" t="inlineStr">
         <is>
-          <t>15→11</t>
+          <t>40→36</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>프로티나</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="B108" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C108" s="11" t="n">
-        <v>270345835</v>
+        <v>275323434</v>
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>2.67%→2.22%</t>
+          <t>6.81%→5.24%</t>
         </is>
       </c>
       <c r="E108" s="13" t="inlineStr">
         <is>
-          <t>22→25</t>
+          <t>55→58</t>
         </is>
       </c>
       <c r="G108" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>와이바이오로직스</t>
         </is>
       </c>
       <c r="H108" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I108" s="15" t="n">
-        <v>-565787064</v>
+        <v>-84951020</v>
       </c>
       <c r="J108" s="16" t="inlineStr">
         <is>
-          <t>7.63%→5.02%</t>
+          <t>0.43%→0.23%</t>
         </is>
       </c>
       <c r="K108" s="13" t="inlineStr">
         <is>
-          <t>40→36</t>
+          <t>15→11</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>HLB이노베이션</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B109" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C109" s="11" t="n">
-        <v>99054216</v>
+        <v>146216965</v>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>3.21%→2.44%</t>
+          <t>6.77%→5.09%</t>
         </is>
       </c>
       <c r="E109" s="13" t="inlineStr">
         <is>
-          <t>72→75</t>
+          <t>103→106</t>
         </is>
       </c>
       <c r="G109" s="14" t="inlineStr">
@@ -4296,23 +4296,23 @@
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>프로티나</t>
         </is>
       </c>
       <c r="B110" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C110" s="11" t="n">
-        <v>146216965</v>
+        <v>270345835</v>
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>6.77%→5.09%</t>
+          <t>2.67%→2.22%</t>
         </is>
       </c>
       <c r="E110" s="13" t="inlineStr">
         <is>
-          <t>103→106</t>
+          <t>22→25</t>
         </is>
       </c>
       <c r="G110" s="17" t="n"/>
@@ -5346,88 +5346,88 @@
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="B140" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C140" s="11" t="n">
-        <v>422450099</v>
+        <v>282200066</v>
       </c>
       <c r="D140" s="12" t="inlineStr">
         <is>
-          <t>0.65%→2.07%</t>
+          <t>3.37%→4.29%</t>
         </is>
       </c>
       <c r="E140" s="13" t="inlineStr">
         <is>
-          <t>9→29</t>
+          <t>70→90</t>
         </is>
       </c>
       <c r="G140" s="14" t="inlineStr">
         <is>
-          <t>덕산하이메탈</t>
+          <t>피엠티</t>
         </is>
       </c>
       <c r="H140" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I140" s="15" t="n">
-        <v>-238000056</v>
+        <v>-71293767</v>
       </c>
       <c r="J140" s="16" t="inlineStr">
         <is>
-          <t>1.46%→0.64%</t>
+          <t>0.26%→0.01%</t>
         </is>
       </c>
       <c r="K140" s="13" t="inlineStr">
         <is>
-          <t>90→40</t>
+          <t>53→3</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="B141" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C141" s="11" t="n">
-        <v>282200066</v>
+        <v>422450099</v>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>3.37%→4.29%</t>
+          <t>0.65%→2.07%</t>
         </is>
       </c>
       <c r="E141" s="13" t="inlineStr">
         <is>
-          <t>70→90</t>
+          <t>9→29</t>
         </is>
       </c>
       <c r="G141" s="14" t="inlineStr">
         <is>
-          <t>피엠티</t>
+          <t>덕산하이메탈</t>
         </is>
       </c>
       <c r="H141" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I141" s="15" t="n">
-        <v>-71293767</v>
+        <v>-238000056</v>
       </c>
       <c r="J141" s="16" t="inlineStr">
         <is>
-          <t>0.26%→0.01%</t>
+          <t>1.46%→0.64%</t>
         </is>
       </c>
       <c r="K141" s="13" t="inlineStr">
         <is>
-          <t>53→3</t>
+          <t>90→40</t>
         </is>
       </c>
     </row>
@@ -5803,23 +5803,23 @@
       <c r="E151" s="17" t="n"/>
       <c r="G151" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>HLB이노베이션</t>
         </is>
       </c>
       <c r="H151" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I151" s="15" t="n">
-        <v>-549312629</v>
+        <v>-74426018</v>
       </c>
       <c r="J151" s="16" t="inlineStr">
         <is>
-          <t>2.89%→1.01%</t>
+          <t>0.92%→0.66%</t>
         </is>
       </c>
       <c r="K151" s="13" t="inlineStr">
         <is>
-          <t>17→6</t>
+          <t>40→29</t>
         </is>
       </c>
     </row>
@@ -5859,23 +5859,23 @@
       <c r="E153" s="17" t="n"/>
       <c r="G153" s="14" t="inlineStr">
         <is>
-          <t>HLB이노베이션</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H153" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I153" s="15" t="n">
-        <v>-74426018</v>
+        <v>-549312629</v>
       </c>
       <c r="J153" s="16" t="inlineStr">
         <is>
-          <t>0.92%→0.66%</t>
+          <t>2.89%→1.01%</t>
         </is>
       </c>
       <c r="K153" s="13" t="inlineStr">
         <is>
-          <t>40→29</t>
+          <t>17→6</t>
         </is>
       </c>
     </row>
@@ -5971,23 +5971,23 @@
       <c r="E157" s="17" t="n"/>
       <c r="G157" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="H157" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I157" s="15" t="n">
-        <v>-172210041</v>
+        <v>-118490028</v>
       </c>
       <c r="J157" s="16" t="inlineStr">
         <is>
-          <t>1.03%→0.44%</t>
+          <t>3.64%→3.20%</t>
         </is>
       </c>
       <c r="K157" s="13" t="inlineStr">
         <is>
-          <t>7→3</t>
+          <t>36→32</t>
         </is>
       </c>
     </row>
@@ -5999,23 +5999,23 @@
       <c r="E158" s="17" t="n"/>
       <c r="G158" s="14" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H158" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I158" s="15" t="n">
-        <v>-118490028</v>
+        <v>-172210041</v>
       </c>
       <c r="J158" s="16" t="inlineStr">
         <is>
-          <t>3.64%→3.20%</t>
+          <t>1.03%→0.44%</t>
         </is>
       </c>
       <c r="K158" s="13" t="inlineStr">
         <is>
-          <t>36→32</t>
+          <t>7→3</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20261026.xlsx
+++ b/reports/pdf_rolling5_20261026.xlsx
@@ -1186,23 +1186,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>403166514</v>
+        <v>2838864800</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>1.43%→1.44%</t>
+          <t>1.45%→2.03%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>173→185</t>
+          <t>25→37</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1230,23 +1230,23 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>2838864800</v>
+        <v>403166514</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>1.45%→2.03%</t>
+          <t>1.43%→1.44%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>25→37</t>
+          <t>173→185</t>
         </is>
       </c>
       <c r="G19" s="17" t="n"/>
@@ -2469,23 +2469,23 @@
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
         <v>-105</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-5391542941</v>
+        <v>-7636864166</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>4.01%→1.80%</t>
+          <t>4.63%→0.85%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>180→75</t>
+          <t>130→25</t>
         </is>
       </c>
     </row>
@@ -2513,23 +2513,23 @@
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-105</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-7636864166</v>
+        <v>-5391542941</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>4.63%→0.85%</t>
+          <t>4.01%→1.80%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>130→25</t>
+          <t>180→75</t>
         </is>
       </c>
     </row>
@@ -3009,23 +3009,23 @@
       <c r="E68" s="17" t="n"/>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H68" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-1584000864</v>
+        <v>-4240502313</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>1.45%→0.74%</t>
+          <t>5.01%→2.78%</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
         <is>
-          <t>50→25</t>
+          <t>60→35</t>
         </is>
       </c>
     </row>
@@ -3065,23 +3065,23 @@
       <c r="E70" s="17" t="n"/>
       <c r="G70" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H70" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I70" s="15" t="n">
-        <v>-4240502313</v>
+        <v>-1584000864</v>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
-          <t>5.01%→2.78%</t>
+          <t>1.45%→0.74%</t>
         </is>
       </c>
       <c r="K70" s="13" t="inlineStr">
         <is>
-          <t>60→35</t>
+          <t>50→25</t>
         </is>
       </c>
     </row>
@@ -4002,23 +4002,23 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>나노신소재</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B99" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C99" s="11" t="n">
-        <v>21427187</v>
+        <v>36710377</v>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>0.12%→0.21%</t>
+          <t>1.84%→1.98%</t>
         </is>
       </c>
       <c r="E99" s="13" t="inlineStr">
         <is>
-          <t>8→14</t>
+          <t>72→78</t>
         </is>
       </c>
       <c r="G99" s="17" t="n"/>
@@ -4030,23 +4030,23 @@
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>나노신소재</t>
         </is>
       </c>
       <c r="B100" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C100" s="11" t="n">
-        <v>36710377</v>
+        <v>21427187</v>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>1.84%→1.98%</t>
+          <t>0.12%→0.21%</t>
         </is>
       </c>
       <c r="E100" s="13" t="inlineStr">
         <is>
-          <t>72→78</t>
+          <t>8→14</t>
         </is>
       </c>
       <c r="G100" s="17" t="n"/>
@@ -4208,23 +4208,23 @@
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>프로티나</t>
         </is>
       </c>
       <c r="B108" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C108" s="11" t="n">
-        <v>275323434</v>
+        <v>270345835</v>
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>6.81%→5.24%</t>
+          <t>2.67%→2.22%</t>
         </is>
       </c>
       <c r="E108" s="13" t="inlineStr">
         <is>
-          <t>55→58</t>
+          <t>22→25</t>
         </is>
       </c>
       <c r="G108" s="14" t="inlineStr">
@@ -4252,23 +4252,23 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="B109" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C109" s="11" t="n">
-        <v>146216965</v>
+        <v>275323434</v>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>6.77%→5.09%</t>
+          <t>6.81%→5.24%</t>
         </is>
       </c>
       <c r="E109" s="13" t="inlineStr">
         <is>
-          <t>103→106</t>
+          <t>55→58</t>
         </is>
       </c>
       <c r="G109" s="14" t="inlineStr">
@@ -4296,23 +4296,23 @@
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>프로티나</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B110" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C110" s="11" t="n">
-        <v>270345835</v>
+        <v>146216965</v>
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>2.67%→2.22%</t>
+          <t>6.77%→5.09%</t>
         </is>
       </c>
       <c r="E110" s="13" t="inlineStr">
         <is>
-          <t>22→25</t>
+          <t>103→106</t>
         </is>
       </c>
       <c r="G110" s="17" t="n"/>
@@ -5118,23 +5118,23 @@
       <c r="E132" s="17" t="n"/>
       <c r="G132" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H132" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I132" s="15" t="n">
-        <v>-273103935</v>
+        <v>-173731959</v>
       </c>
       <c r="J132" s="16" t="inlineStr">
         <is>
-          <t>4.46%→3.93%</t>
+          <t>2.57%→2.14%</t>
         </is>
       </c>
       <c r="K132" s="13" t="inlineStr">
         <is>
-          <t>53→49</t>
+          <t>46→42</t>
         </is>
       </c>
     </row>
@@ -5146,23 +5146,23 @@
       <c r="E133" s="17" t="n"/>
       <c r="G133" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="H133" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I133" s="15" t="n">
-        <v>-173731959</v>
+        <v>-273103935</v>
       </c>
       <c r="J133" s="16" t="inlineStr">
         <is>
-          <t>2.57%→2.14%</t>
+          <t>4.46%→3.93%</t>
         </is>
       </c>
       <c r="K133" s="13" t="inlineStr">
         <is>
-          <t>46→42</t>
+          <t>53→49</t>
         </is>
       </c>
     </row>
@@ -5346,88 +5346,88 @@
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="B140" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C140" s="11" t="n">
-        <v>282200066</v>
+        <v>422450099</v>
       </c>
       <c r="D140" s="12" t="inlineStr">
         <is>
-          <t>3.37%→4.29%</t>
+          <t>0.65%→2.07%</t>
         </is>
       </c>
       <c r="E140" s="13" t="inlineStr">
         <is>
-          <t>70→90</t>
+          <t>9→29</t>
         </is>
       </c>
       <c r="G140" s="14" t="inlineStr">
         <is>
-          <t>피엠티</t>
+          <t>덕산하이메탈</t>
         </is>
       </c>
       <c r="H140" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I140" s="15" t="n">
-        <v>-71293767</v>
+        <v>-238000056</v>
       </c>
       <c r="J140" s="16" t="inlineStr">
         <is>
-          <t>0.26%→0.01%</t>
+          <t>1.46%→0.64%</t>
         </is>
       </c>
       <c r="K140" s="13" t="inlineStr">
         <is>
-          <t>53→3</t>
+          <t>90→40</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="B141" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C141" s="11" t="n">
-        <v>422450099</v>
+        <v>282200066</v>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>0.65%→2.07%</t>
+          <t>3.37%→4.29%</t>
         </is>
       </c>
       <c r="E141" s="13" t="inlineStr">
         <is>
-          <t>9→29</t>
+          <t>70→90</t>
         </is>
       </c>
       <c r="G141" s="14" t="inlineStr">
         <is>
-          <t>덕산하이메탈</t>
+          <t>피엠티</t>
         </is>
       </c>
       <c r="H141" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I141" s="15" t="n">
-        <v>-238000056</v>
+        <v>-71293767</v>
       </c>
       <c r="J141" s="16" t="inlineStr">
         <is>
-          <t>1.46%→0.64%</t>
+          <t>0.26%→0.01%</t>
         </is>
       </c>
       <c r="K141" s="13" t="inlineStr">
         <is>
-          <t>90→40</t>
+          <t>53→3</t>
         </is>
       </c>
     </row>
@@ -5803,23 +5803,23 @@
       <c r="E151" s="17" t="n"/>
       <c r="G151" s="14" t="inlineStr">
         <is>
-          <t>HLB이노베이션</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H151" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I151" s="15" t="n">
-        <v>-74426018</v>
+        <v>-549312629</v>
       </c>
       <c r="J151" s="16" t="inlineStr">
         <is>
-          <t>0.92%→0.66%</t>
+          <t>2.89%→1.01%</t>
         </is>
       </c>
       <c r="K151" s="13" t="inlineStr">
         <is>
-          <t>40→29</t>
+          <t>17→6</t>
         </is>
       </c>
     </row>
@@ -5831,23 +5831,23 @@
       <c r="E152" s="17" t="n"/>
       <c r="G152" s="14" t="inlineStr">
         <is>
-          <t>네패스</t>
+          <t>HLB이노베이션</t>
         </is>
       </c>
       <c r="H152" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I152" s="15" t="n">
-        <v>-108927526</v>
+        <v>-74426018</v>
       </c>
       <c r="J152" s="16" t="inlineStr">
         <is>
-          <t>0.91%→0.54%</t>
+          <t>0.92%→0.66%</t>
         </is>
       </c>
       <c r="K152" s="13" t="inlineStr">
         <is>
-          <t>27→16</t>
+          <t>40→29</t>
         </is>
       </c>
     </row>
@@ -5859,23 +5859,23 @@
       <c r="E153" s="17" t="n"/>
       <c r="G153" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>네패스</t>
         </is>
       </c>
       <c r="H153" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I153" s="15" t="n">
-        <v>-549312629</v>
+        <v>-108927526</v>
       </c>
       <c r="J153" s="16" t="inlineStr">
         <is>
-          <t>2.89%→1.01%</t>
+          <t>0.91%→0.54%</t>
         </is>
       </c>
       <c r="K153" s="13" t="inlineStr">
         <is>
-          <t>17→6</t>
+          <t>27→16</t>
         </is>
       </c>
     </row>
@@ -5971,23 +5971,23 @@
       <c r="E157" s="17" t="n"/>
       <c r="G157" s="14" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H157" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I157" s="15" t="n">
-        <v>-118490028</v>
+        <v>-172210041</v>
       </c>
       <c r="J157" s="16" t="inlineStr">
         <is>
-          <t>3.64%→3.20%</t>
+          <t>1.03%→0.44%</t>
         </is>
       </c>
       <c r="K157" s="13" t="inlineStr">
         <is>
-          <t>36→32</t>
+          <t>7→3</t>
         </is>
       </c>
     </row>
@@ -5999,23 +5999,23 @@
       <c r="E158" s="17" t="n"/>
       <c r="G158" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="H158" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I158" s="15" t="n">
-        <v>-172210041</v>
+        <v>-118490028</v>
       </c>
       <c r="J158" s="16" t="inlineStr">
         <is>
-          <t>1.03%→0.44%</t>
+          <t>3.64%→3.20%</t>
         </is>
       </c>
       <c r="K158" s="13" t="inlineStr">
         <is>
-          <t>7→3</t>
+          <t>36→32</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20261026.xlsx
+++ b/reports/pdf_rolling5_20261026.xlsx
@@ -1186,23 +1186,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>2838864800</v>
+        <v>560019758</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>1.45%→2.03%</t>
+          <t>0.43%→0.50%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>25→37</t>
+          <t>34→46</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1230,23 +1230,23 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>403166514</v>
+        <v>2838864800</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>1.43%→1.44%</t>
+          <t>1.45%→2.03%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>173→185</t>
+          <t>25→37</t>
         </is>
       </c>
       <c r="G19" s="17" t="n"/>
@@ -1258,23 +1258,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>560019758</v>
+        <v>403166514</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>0.43%→0.50%</t>
+          <t>1.43%→1.44%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>34→46</t>
+          <t>173→185</t>
         </is>
       </c>
       <c r="G20" s="17" t="n"/>
@@ -2689,23 +2689,23 @@
       </c>
       <c r="G60" s="14" t="inlineStr">
         <is>
-          <t>비츠로셀  (편출)</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H60" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-795300434</v>
+        <v>-5936703238</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>0.34%→0.00%</t>
+          <t>6.50%→3.34%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>110→60</t>
         </is>
       </c>
     </row>
@@ -2733,23 +2733,23 @@
       </c>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>비츠로셀  (편출)</t>
         </is>
       </c>
       <c r="H61" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-5936703238</v>
+        <v>-795300434</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>6.50%→3.34%</t>
+          <t>0.34%→0.00%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
         <is>
-          <t>110→60</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
@@ -2777,23 +2777,23 @@
       </c>
       <c r="G62" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="H62" s="15" t="n">
         <v>-49</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-3279277789</v>
+        <v>-2121505157</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>2.86%→1.25%</t>
+          <t>1.91%→1.01%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
         <is>
-          <t>89→40</t>
+          <t>99→50</t>
         </is>
       </c>
     </row>
@@ -2821,46 +2821,46 @@
       </c>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H63" s="15" t="n">
         <v>-49</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-2121505157</v>
+        <v>-3279277789</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>1.91%→1.01%</t>
+          <t>2.86%→1.25%</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
         <is>
-          <t>99→50</t>
+          <t>89→40</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B64" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>1002870547</v>
+        <v>1715670936</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>0.47%→0.91%</t>
+          <t>5.87%→6.43%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>14→29</t>
+          <t>105→120</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
@@ -2888,23 +2888,23 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B65" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>1715670936</v>
+        <v>1002870547</v>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>5.87%→6.43%</t>
+          <t>0.47%→0.91%</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
-          <t>105→120</t>
+          <t>14→29</t>
         </is>
       </c>
       <c r="G65" s="14" t="inlineStr">
@@ -3037,23 +3037,23 @@
       <c r="E69" s="17" t="n"/>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오  (편출)</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H69" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-715275390</v>
+        <v>-1584000864</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>0.30%→0.00%</t>
+          <t>1.45%→0.74%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
         <is>
-          <t>25→0</t>
+          <t>50→25</t>
         </is>
       </c>
     </row>
@@ -3065,23 +3065,23 @@
       <c r="E70" s="17" t="n"/>
       <c r="G70" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>에이비엘바이오  (편출)</t>
         </is>
       </c>
       <c r="H70" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I70" s="15" t="n">
-        <v>-1584000864</v>
+        <v>-715275390</v>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
-          <t>1.45%→0.74%</t>
+          <t>0.30%→0.00%</t>
         </is>
       </c>
       <c r="K70" s="13" t="inlineStr">
         <is>
-          <t>50→25</t>
+          <t>25→0</t>
         </is>
       </c>
     </row>
@@ -3205,23 +3205,23 @@
       <c r="E75" s="17" t="n"/>
       <c r="G75" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>보로노이  (편출)</t>
         </is>
       </c>
       <c r="H75" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I75" s="15" t="n">
-        <v>-1861201015</v>
+        <v>-650496355</v>
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
-          <t>2.67%→2.07%</t>
+          <t>0.28%→0.00%</t>
         </is>
       </c>
       <c r="K75" s="13" t="inlineStr">
         <is>
-          <t>27→19</t>
+          <t>8→0</t>
         </is>
       </c>
     </row>
@@ -3233,23 +3233,23 @@
       <c r="E76" s="17" t="n"/>
       <c r="G76" s="14" t="inlineStr">
         <is>
-          <t>보로노이  (편출)</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H76" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I76" s="15" t="n">
-        <v>-650496355</v>
+        <v>-1861201015</v>
       </c>
       <c r="J76" s="16" t="inlineStr">
         <is>
-          <t>0.28%→0.00%</t>
+          <t>2.67%→2.07%</t>
         </is>
       </c>
       <c r="K76" s="13" t="inlineStr">
         <is>
-          <t>8→0</t>
+          <t>27→19</t>
         </is>
       </c>
     </row>
@@ -3914,23 +3914,23 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>선익시스템</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B97" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C97" s="11" t="n">
-        <v>38079976</v>
+        <v>49369569</v>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>1.32%→1.46%</t>
+          <t>2.26%→2.45%</t>
         </is>
       </c>
       <c r="E97" s="13" t="inlineStr">
         <is>
-          <t>58→65</t>
+          <t>77→84</t>
         </is>
       </c>
       <c r="G97" s="14" t="inlineStr">
@@ -3958,23 +3958,23 @@
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>선익시스템</t>
         </is>
       </c>
       <c r="B98" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C98" s="11" t="n">
-        <v>49369569</v>
+        <v>38079976</v>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>2.26%→2.45%</t>
+          <t>1.32%→1.46%</t>
         </is>
       </c>
       <c r="E98" s="13" t="inlineStr">
         <is>
-          <t>77→84</t>
+          <t>58→65</t>
         </is>
       </c>
       <c r="G98" s="14" t="inlineStr">
@@ -4185,90 +4185,90 @@
       </c>
       <c r="G107" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>와이바이오로직스</t>
         </is>
       </c>
       <c r="H107" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I107" s="15" t="n">
-        <v>-565787064</v>
+        <v>-84951020</v>
       </c>
       <c r="J107" s="16" t="inlineStr">
         <is>
-          <t>7.63%→5.02%</t>
+          <t>0.43%→0.23%</t>
         </is>
       </c>
       <c r="K107" s="13" t="inlineStr">
         <is>
-          <t>40→36</t>
+          <t>15→11</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>프로티나</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B108" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C108" s="11" t="n">
-        <v>270345835</v>
+        <v>146216965</v>
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>2.67%→2.22%</t>
+          <t>6.77%→5.09%</t>
         </is>
       </c>
       <c r="E108" s="13" t="inlineStr">
         <is>
-          <t>22→25</t>
+          <t>103→106</t>
         </is>
       </c>
       <c r="G108" s="14" t="inlineStr">
         <is>
-          <t>와이바이오로직스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H108" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I108" s="15" t="n">
-        <v>-84951020</v>
+        <v>-565787064</v>
       </c>
       <c r="J108" s="16" t="inlineStr">
         <is>
-          <t>0.43%→0.23%</t>
+          <t>7.63%→5.02%</t>
         </is>
       </c>
       <c r="K108" s="13" t="inlineStr">
         <is>
-          <t>15→11</t>
+          <t>40→36</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>프로티나</t>
         </is>
       </c>
       <c r="B109" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C109" s="11" t="n">
-        <v>275323434</v>
+        <v>270345835</v>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>6.81%→5.24%</t>
+          <t>2.67%→2.22%</t>
         </is>
       </c>
       <c r="E109" s="13" t="inlineStr">
         <is>
-          <t>55→58</t>
+          <t>22→25</t>
         </is>
       </c>
       <c r="G109" s="14" t="inlineStr">
@@ -4296,23 +4296,23 @@
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="B110" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C110" s="11" t="n">
-        <v>146216965</v>
+        <v>275323434</v>
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>6.77%→5.09%</t>
+          <t>6.81%→5.24%</t>
         </is>
       </c>
       <c r="E110" s="13" t="inlineStr">
         <is>
-          <t>103→106</t>
+          <t>55→58</t>
         </is>
       </c>
       <c r="G110" s="17" t="n"/>
@@ -5346,23 +5346,23 @@
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="B140" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C140" s="11" t="n">
-        <v>422450099</v>
+        <v>282200066</v>
       </c>
       <c r="D140" s="12" t="inlineStr">
         <is>
-          <t>0.65%→2.07%</t>
+          <t>3.37%→4.29%</t>
         </is>
       </c>
       <c r="E140" s="13" t="inlineStr">
         <is>
-          <t>9→29</t>
+          <t>70→90</t>
         </is>
       </c>
       <c r="G140" s="14" t="inlineStr">
@@ -5390,23 +5390,23 @@
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="B141" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C141" s="11" t="n">
-        <v>282200066</v>
+        <v>422450099</v>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>3.37%→4.29%</t>
+          <t>0.65%→2.07%</t>
         </is>
       </c>
       <c r="E141" s="13" t="inlineStr">
         <is>
-          <t>70→90</t>
+          <t>9→29</t>
         </is>
       </c>
       <c r="G141" s="14" t="inlineStr">
@@ -5522,23 +5522,23 @@
     <row r="144">
       <c r="A144" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>선익시스템  (신규)</t>
         </is>
       </c>
       <c r="B144" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>89887521</v>
+        <v>325125076</v>
       </c>
       <c r="D144" s="12" t="inlineStr">
         <is>
-          <t>0.72%→1.01%</t>
+          <t>0.00%→1.10%</t>
         </is>
       </c>
       <c r="E144" s="13" t="inlineStr">
         <is>
-          <t>21→30</t>
+          <t>0→9</t>
         </is>
       </c>
       <c r="G144" s="14" t="inlineStr">
@@ -5566,23 +5566,23 @@
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>선익시스템  (신규)</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B145" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C145" s="11" t="n">
-        <v>325125076</v>
+        <v>89887521</v>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.10%</t>
+          <t>0.72%→1.01%</t>
         </is>
       </c>
       <c r="E145" s="13" t="inlineStr">
         <is>
-          <t>0→9</t>
+          <t>21→30</t>
         </is>
       </c>
       <c r="G145" s="14" t="inlineStr">
@@ -5803,23 +5803,23 @@
       <c r="E151" s="17" t="n"/>
       <c r="G151" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>네패스</t>
         </is>
       </c>
       <c r="H151" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I151" s="15" t="n">
-        <v>-549312629</v>
+        <v>-108927526</v>
       </c>
       <c r="J151" s="16" t="inlineStr">
         <is>
-          <t>2.89%→1.01%</t>
+          <t>0.91%→0.54%</t>
         </is>
       </c>
       <c r="K151" s="13" t="inlineStr">
         <is>
-          <t>17→6</t>
+          <t>27→16</t>
         </is>
       </c>
     </row>
@@ -5831,23 +5831,23 @@
       <c r="E152" s="17" t="n"/>
       <c r="G152" s="14" t="inlineStr">
         <is>
-          <t>HLB이노베이션</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H152" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I152" s="15" t="n">
-        <v>-74426018</v>
+        <v>-549312629</v>
       </c>
       <c r="J152" s="16" t="inlineStr">
         <is>
-          <t>0.92%→0.66%</t>
+          <t>2.89%→1.01%</t>
         </is>
       </c>
       <c r="K152" s="13" t="inlineStr">
         <is>
-          <t>40→29</t>
+          <t>17→6</t>
         </is>
       </c>
     </row>
@@ -5859,23 +5859,23 @@
       <c r="E153" s="17" t="n"/>
       <c r="G153" s="14" t="inlineStr">
         <is>
-          <t>네패스</t>
+          <t>HLB이노베이션</t>
         </is>
       </c>
       <c r="H153" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I153" s="15" t="n">
-        <v>-108927526</v>
+        <v>-74426018</v>
       </c>
       <c r="J153" s="16" t="inlineStr">
         <is>
-          <t>0.91%→0.54%</t>
+          <t>0.92%→0.66%</t>
         </is>
       </c>
       <c r="K153" s="13" t="inlineStr">
         <is>
-          <t>27→16</t>
+          <t>40→29</t>
         </is>
       </c>
     </row>
